--- a/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
+++ b/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
@@ -1041,6 +1041,12 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1060,12 +1066,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1397,41 +1397,41 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" thickBot="1"/>
     <row r="2" spans="1:12" ht="53.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="64"/>
     </row>
     <row r="3" spans="1:12" ht="18.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="34.5" customHeight="1">
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
@@ -1652,7 +1652,7 @@
       <c r="G11" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="H11" s="64"/>
+      <c r="H11" s="57"/>
       <c r="I11" s="50" t="s">
         <v>40</v>
       </c>
@@ -1665,69 +1665,69 @@
       <c r="L11" s="54"/>
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="A12" s="34"/>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="49">
         <v>45859</v>
       </c>
-      <c r="D12" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="36">
+      <c r="D12" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="49">
         <v>45863</v>
       </c>
-      <c r="F12" s="38">
+      <c r="F12" s="51">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G12" s="33" t="s">
+      <c r="G12" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="H12" s="63"/>
-      <c r="I12" s="37" t="s">
+      <c r="H12" s="52"/>
+      <c r="I12" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="J12" s="39" t="s">
+      <c r="J12" s="53" t="s">
         <v>112</v>
       </c>
-      <c r="K12" s="39" t="s">
+      <c r="K12" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="L12" s="40"/>
+      <c r="L12" s="54"/>
     </row>
     <row r="13" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B13" s="17" t="s">
+      <c r="A13" s="34"/>
+      <c r="B13" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="36">
         <v>45866</v>
       </c>
-      <c r="D13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="18">
+      <c r="D13" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="36">
         <v>45867</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="38">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="H13" s="21"/>
-      <c r="I13" s="19" t="s">
+      <c r="H13" s="56"/>
+      <c r="I13" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="J13" s="22" t="s">
+      <c r="J13" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="K13" s="22" t="s">
+      <c r="K13" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="L13" s="23"/>
+      <c r="L13" s="40"/>
     </row>
     <row r="14" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B14" s="17" t="s">
@@ -2274,32 +2274,32 @@
       </c>
     </row>
     <row r="31" spans="2:12" ht="21.75" customHeight="1">
-      <c r="B31" s="58" t="s">
+      <c r="B31" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="58"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="60"/>
+      <c r="K31" s="60"/>
     </row>
     <row r="32" spans="2:12" s="5" customFormat="1" ht="26.25">
-      <c r="B32" s="59" t="s">
+      <c r="B32" s="61" t="s">
         <v>87</v>
       </c>
-      <c r="C32" s="59"/>
-      <c r="D32" s="59"/>
-      <c r="E32" s="59"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="59"/>
-      <c r="I32" s="59"/>
-      <c r="J32" s="59"/>
-      <c r="K32" s="59"/>
+      <c r="C32" s="61"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="61"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="61"/>
     </row>
     <row r="43" spans="9:9">
       <c r="I43" s="2" t="s">

--- a/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
+++ b/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
@@ -641,7 +641,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -708,6 +708,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -993,9 +999,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1041,9 +1044,6 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1067,6 +1067,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1397,41 +1403,41 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" thickBot="1"/>
     <row r="2" spans="1:12" ht="53.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63"/>
-      <c r="K2" s="63"/>
-      <c r="L2" s="64"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="62"/>
     </row>
     <row r="3" spans="1:12" ht="18.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="34.5" customHeight="1">
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
@@ -1539,229 +1545,229 @@
       <c r="L7" s="15"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="42">
+      <c r="C8" s="41">
         <v>45834</v>
       </c>
-      <c r="D8" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="42">
+      <c r="D8" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="41">
         <v>45835</v>
       </c>
-      <c r="F8" s="44">
+      <c r="F8" s="43">
         <f>DAYS360(C8,E8)+1</f>
         <v>2</v>
       </c>
-      <c r="G8" s="45" t="s">
+      <c r="G8" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="46" t="s">
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="L8" s="47" t="s">
+      <c r="L8" s="46" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="49">
+      <c r="C9" s="48">
         <v>45838</v>
       </c>
-      <c r="D9" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="49">
+      <c r="D9" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="48">
         <v>45842</v>
       </c>
-      <c r="F9" s="51">
+      <c r="F9" s="50">
         <f t="shared" ref="F9:F27" si="0">DAYS360(C9,E9)+1</f>
         <v>5</v>
       </c>
-      <c r="G9" s="45" t="s">
+      <c r="G9" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="52"/>
-      <c r="I9" s="50" t="s">
+      <c r="H9" s="51"/>
+      <c r="I9" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="50" t="s">
+      <c r="J9" s="49" t="s">
         <v>93</v>
       </c>
-      <c r="K9" s="53" t="s">
+      <c r="K9" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="L9" s="54"/>
+      <c r="L9" s="53"/>
     </row>
     <row r="10" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="49">
+      <c r="C10" s="48">
         <v>45845</v>
       </c>
-      <c r="D10" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="49">
+      <c r="D10" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="48">
         <v>45849</v>
       </c>
-      <c r="F10" s="51">
+      <c r="F10" s="50">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G10" s="45" t="s">
+      <c r="G10" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="H10" s="52"/>
-      <c r="I10" s="50" t="s">
+      <c r="H10" s="51"/>
+      <c r="I10" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="J10" s="50" t="s">
+      <c r="J10" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="K10" s="53" t="s">
+      <c r="K10" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="L10" s="54"/>
+      <c r="L10" s="53"/>
     </row>
     <row r="11" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="49">
+      <c r="C11" s="48">
         <v>45852</v>
       </c>
-      <c r="D11" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="49">
+      <c r="D11" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="48">
         <v>45856</v>
       </c>
-      <c r="F11" s="51">
+      <c r="F11" s="50">
         <f>DAYS360(C11,E11)+1</f>
         <v>5</v>
       </c>
-      <c r="G11" s="45" t="s">
+      <c r="G11" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="H11" s="57"/>
-      <c r="I11" s="50" t="s">
+      <c r="H11" s="55"/>
+      <c r="I11" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="J11" s="53" t="s">
+      <c r="J11" s="52" t="s">
         <v>110</v>
       </c>
-      <c r="K11" s="53" t="s">
+      <c r="K11" s="52" t="s">
         <v>96</v>
       </c>
-      <c r="L11" s="54"/>
+      <c r="L11" s="53"/>
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="49">
+      <c r="C12" s="48">
         <v>45859</v>
       </c>
-      <c r="D12" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="49">
+      <c r="D12" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="48">
         <v>45863</v>
       </c>
-      <c r="F12" s="51">
+      <c r="F12" s="50">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G12" s="45" t="s">
+      <c r="G12" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="H12" s="52"/>
-      <c r="I12" s="50" t="s">
+      <c r="H12" s="51"/>
+      <c r="I12" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="J12" s="53" t="s">
+      <c r="J12" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="K12" s="53" t="s">
+      <c r="K12" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="L12" s="54"/>
+      <c r="L12" s="53"/>
     </row>
     <row r="13" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="A13" s="34"/>
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="48">
         <v>45866</v>
       </c>
-      <c r="D13" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="36">
+      <c r="D13" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="48">
         <v>45867</v>
       </c>
-      <c r="F13" s="38">
+      <c r="F13" s="50">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G13" s="33" t="s">
+      <c r="G13" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="H13" s="56"/>
-      <c r="I13" s="37" t="s">
+      <c r="H13" s="51"/>
+      <c r="I13" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="J13" s="39" t="s">
+      <c r="J13" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="K13" s="39" t="s">
+      <c r="K13" s="52" t="s">
         <v>111</v>
       </c>
-      <c r="L13" s="40"/>
+      <c r="L13" s="53"/>
     </row>
     <row r="14" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B14" s="17" t="s">
+      <c r="A14" s="34"/>
+      <c r="B14" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="36">
         <v>45873</v>
       </c>
-      <c r="D14" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="18">
+      <c r="D14" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="36">
         <v>45877</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="38">
         <f>DAYS360(C14,E14)+1</f>
         <v>5</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="30" t="s">
+      <c r="H14" s="64" t="s">
         <v>58</v>
       </c>
-      <c r="I14" s="22" t="s">
+      <c r="I14" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="J14" s="22" t="s">
+      <c r="J14" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="K14" s="22" t="s">
+      <c r="K14" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="L14" s="24"/>
+      <c r="L14" s="63"/>
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B15" s="17" t="s">
@@ -1853,7 +1859,7 @@
       <c r="I17" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="J17" s="55" t="s">
+      <c r="J17" s="54" t="s">
         <v>109</v>
       </c>
       <c r="K17" s="22" t="s">
@@ -1987,7 +1993,7 @@
       <c r="I21" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="J21" s="55" t="s">
+      <c r="J21" s="54" t="s">
         <v>104</v>
       </c>
       <c r="K21" s="22" t="s">
@@ -2274,32 +2280,32 @@
       </c>
     </row>
     <row r="31" spans="2:12" ht="21.75" customHeight="1">
-      <c r="B31" s="60" t="s">
+      <c r="B31" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="60"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="60"/>
-      <c r="F31" s="60"/>
-      <c r="G31" s="60"/>
-      <c r="H31" s="60"/>
-      <c r="I31" s="60"/>
-      <c r="J31" s="60"/>
-      <c r="K31" s="60"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="58"/>
     </row>
     <row r="32" spans="2:12" s="5" customFormat="1" ht="26.25">
-      <c r="B32" s="61" t="s">
+      <c r="B32" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="C32" s="61"/>
-      <c r="D32" s="61"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="61"/>
-      <c r="J32" s="61"/>
-      <c r="K32" s="61"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="59"/>
+      <c r="H32" s="59"/>
+      <c r="I32" s="59"/>
+      <c r="J32" s="59"/>
+      <c r="K32" s="59"/>
     </row>
     <row r="43" spans="9:9">
       <c r="I43" s="2" t="s">

--- a/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
+++ b/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\웹퍼블리셔과정_탐\github\WPC-626-TOM\001.일정관리\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494AFD33-F834-41F5-A3C5-7FA30A6197F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13740"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hi-Media 반응형 웹퍼블리셔 1회차 주별 상세일정" sheetId="1" r:id="rId1"/>
@@ -185,10 +191,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>도깨비 PJ 상세코딩 / CGV PJ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>도깨비 PJ 상세코딩</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -519,19 +521,23 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>도깨비 PJ 상세코딩 / CGV PJ
+    <t>도깨비 PJ UI 디자인</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>도깨비 PJ UI 디자인
 과목평가제출주간(금요일까지)</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>도깨비 PJ 프로토타이핑</t>
+    <t>도깨비 PJ 프로토타이핑 / 상세코딩</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="#\ &quot;일&quot;"/>
     <numFmt numFmtId="177" formatCode="&quot;총&quot;\ #\ &quot;일&quot;"/>
@@ -1047,6 +1053,12 @@
     <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1067,19 +1079,13 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2" xfId="2"/>
-    <cellStyle name="표준 3" xfId="3"/>
-    <cellStyle name="표준 4" xfId="1"/>
+    <cellStyle name="표준 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="표준 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="표준 4" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1137,7 +1143,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1170,9 +1176,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1205,6 +1228,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1380,7 +1420,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1403,41 +1443,41 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" thickBot="1"/>
     <row r="2" spans="1:12" ht="53.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="60" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="62"/>
+      <c r="B2" s="62" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="64"/>
     </row>
     <row r="3" spans="1:12" ht="18.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="34.5" customHeight="1">
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
@@ -1445,7 +1485,7 @@
         <v>10</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>31</v>
@@ -1562,16 +1602,16 @@
         <v>2</v>
       </c>
       <c r="G8" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H8" s="42"/>
       <c r="I8" s="42"/>
       <c r="J8" s="42"/>
       <c r="K8" s="45" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L8" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
@@ -1592,17 +1632,17 @@
         <v>5</v>
       </c>
       <c r="G9" s="44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H9" s="51"/>
       <c r="I9" s="49" t="s">
         <v>41</v>
       </c>
       <c r="J9" s="49" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K9" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L9" s="53"/>
     </row>
@@ -1624,17 +1664,17 @@
         <v>5</v>
       </c>
       <c r="G10" s="44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H10" s="51"/>
       <c r="I10" s="49" t="s">
         <v>40</v>
       </c>
       <c r="J10" s="49" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K10" s="52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L10" s="53"/>
     </row>
@@ -1656,17 +1696,17 @@
         <v>5</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H11" s="55"/>
       <c r="I11" s="49" t="s">
         <v>40</v>
       </c>
       <c r="J11" s="52" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K11" s="52" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L11" s="53"/>
     </row>
@@ -1688,17 +1728,17 @@
         <v>5</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H12" s="51"/>
       <c r="I12" s="49" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J12" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K12" s="52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L12" s="53"/>
     </row>
@@ -1720,17 +1760,17 @@
         <v>2</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H13" s="51"/>
       <c r="I13" s="49" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="J13" s="52" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K13" s="52" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L13" s="53"/>
     </row>
@@ -1753,21 +1793,21 @@
         <v>5</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="H14" s="64" t="s">
         <v>58</v>
+      </c>
+      <c r="H14" s="57" t="s">
+        <v>57</v>
       </c>
       <c r="I14" s="39" t="s">
         <v>113</v>
       </c>
       <c r="J14" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K14" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="L14" s="63"/>
+        <v>97</v>
+      </c>
+      <c r="L14" s="56"/>
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B15" s="17" t="s">
@@ -1787,17 +1827,17 @@
         <v>4</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H15" s="21"/>
       <c r="I15" s="22" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="J15" s="19" t="s">
         <v>33</v>
       </c>
       <c r="K15" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L15" s="23"/>
     </row>
@@ -1819,17 +1859,17 @@
         <v>5</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H16" s="21"/>
       <c r="I16" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J16" s="19" t="s">
         <v>39</v>
       </c>
       <c r="K16" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L16" s="23"/>
     </row>
@@ -1851,22 +1891,22 @@
         <v>5</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H17" s="30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I17" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J17" s="54" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K17" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L17" s="28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
@@ -1887,17 +1927,17 @@
         <v>5</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H18" s="21"/>
       <c r="I18" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K18" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L18" s="23"/>
     </row>
@@ -1919,19 +1959,19 @@
         <v>5</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H19" s="30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K19" s="22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L19" s="23"/>
     </row>
@@ -1953,19 +1993,19 @@
         <v>5</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H20" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I20" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K20" s="22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L20" s="23"/>
     </row>
@@ -1987,17 +2027,17 @@
         <v>5</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H21" s="21"/>
       <c r="I21" s="22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J21" s="54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K21" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L21" s="23"/>
     </row>
@@ -2019,17 +2059,17 @@
         <v>4</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H22" s="21"/>
       <c r="I22" s="22" t="s">
         <v>43</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K22" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L22" s="23"/>
     </row>
@@ -2051,17 +2091,17 @@
         <v>1</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H23" s="21"/>
       <c r="I23" s="22" t="s">
         <v>43</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K23" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L23" s="23"/>
     </row>
@@ -2083,19 +2123,19 @@
         <v>5</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H24" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I24" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K24" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L24" s="23"/>
     </row>
@@ -2117,19 +2157,19 @@
         <v>5</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H25" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I25" s="21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K25" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L25" s="23"/>
     </row>
@@ -2151,22 +2191,22 @@
         <v>5</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H26" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I26" s="21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K26" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L26" s="29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="2:12" ht="56.45" customHeight="1">
@@ -2187,19 +2227,19 @@
         <v>5</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H27" s="30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J27" s="19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K27" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L27" s="25"/>
     </row>
@@ -2221,17 +2261,17 @@
         <v>5</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H28" s="26"/>
       <c r="I28" s="21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J28" s="19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K28" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L28" s="24"/>
     </row>
@@ -2253,22 +2293,22 @@
         <v>2</v>
       </c>
       <c r="G29" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="H29" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="I29" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="J29" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="L29" s="27" t="s">
         <v>76</v>
-      </c>
-      <c r="H29" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="I29" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="J29" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="K29" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="L29" s="27" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="30" spans="2:12" ht="47.25" customHeight="1" thickBot="1">
@@ -2280,32 +2320,32 @@
       </c>
     </row>
     <row r="31" spans="2:12" ht="21.75" customHeight="1">
-      <c r="B31" s="58" t="s">
+      <c r="B31" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="58"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="60"/>
+      <c r="K31" s="60"/>
     </row>
     <row r="32" spans="2:12" s="5" customFormat="1" ht="26.25">
-      <c r="B32" s="59" t="s">
-        <v>87</v>
-      </c>
-      <c r="C32" s="59"/>
-      <c r="D32" s="59"/>
-      <c r="E32" s="59"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="59"/>
-      <c r="I32" s="59"/>
-      <c r="J32" s="59"/>
-      <c r="K32" s="59"/>
+      <c r="B32" s="61" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" s="61"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="61"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="61"/>
     </row>
     <row r="43" spans="9:9">
       <c r="I43" s="2" t="s">
@@ -2327,7 +2367,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData/>
@@ -2337,7 +2377,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData/>

--- a/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
+++ b/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\웹퍼블리셔과정_탐\github\WPC-626-TOM\001.일정관리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494AFD33-F834-41F5-A3C5-7FA30A6197F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D020DC-DF03-4AFD-9432-C3FF69A52584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -647,7 +647,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -714,12 +714,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -884,7 +878,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1053,12 +1047,6 @@
     <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1079,6 +1067,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1443,41 +1440,41 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" thickBot="1"/>
     <row r="2" spans="1:12" ht="53.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63"/>
-      <c r="K2" s="63"/>
-      <c r="L2" s="64"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="62"/>
     </row>
     <row r="3" spans="1:12" ht="18.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="34.5" customHeight="1">
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
@@ -1775,71 +1772,71 @@
       <c r="L13" s="53"/>
     </row>
     <row r="14" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="A14" s="34"/>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="48">
         <v>45873</v>
       </c>
-      <c r="D14" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="36">
+      <c r="D14" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="48">
         <v>45877</v>
       </c>
-      <c r="F14" s="38">
+      <c r="F14" s="50">
         <f>DAYS360(C14,E14)+1</f>
         <v>5</v>
       </c>
-      <c r="G14" s="33" t="s">
+      <c r="G14" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="H14" s="57" t="s">
+      <c r="H14" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="I14" s="39" t="s">
+      <c r="I14" s="52" t="s">
         <v>113</v>
       </c>
-      <c r="J14" s="39" t="s">
+      <c r="J14" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="K14" s="39" t="s">
+      <c r="K14" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="L14" s="56"/>
+      <c r="L14" s="46"/>
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B15" s="17" t="s">
+      <c r="A15" s="34"/>
+      <c r="B15" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="36">
         <v>45880</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="18">
+      <c r="D15" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="36">
         <v>45883</v>
       </c>
-      <c r="F15" s="32">
+      <c r="F15" s="38">
         <f>DAYS360(C15,E15)+1</f>
         <v>4</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="H15" s="21"/>
-      <c r="I15" s="22" t="s">
+      <c r="H15" s="63"/>
+      <c r="I15" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="J15" s="19" t="s">
+      <c r="J15" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="K15" s="22" t="s">
+      <c r="K15" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="L15" s="23"/>
+      <c r="L15" s="64"/>
     </row>
     <row r="16" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B16" s="17" t="s">
@@ -2320,32 +2317,32 @@
       </c>
     </row>
     <row r="31" spans="2:12" ht="21.75" customHeight="1">
-      <c r="B31" s="60" t="s">
+      <c r="B31" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="60"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="60"/>
-      <c r="F31" s="60"/>
-      <c r="G31" s="60"/>
-      <c r="H31" s="60"/>
-      <c r="I31" s="60"/>
-      <c r="J31" s="60"/>
-      <c r="K31" s="60"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="58"/>
     </row>
     <row r="32" spans="2:12" s="5" customFormat="1" ht="26.25">
-      <c r="B32" s="61" t="s">
+      <c r="B32" s="59" t="s">
         <v>86</v>
       </c>
-      <c r="C32" s="61"/>
-      <c r="D32" s="61"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="61"/>
-      <c r="J32" s="61"/>
-      <c r="K32" s="61"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="59"/>
+      <c r="H32" s="59"/>
+      <c r="I32" s="59"/>
+      <c r="J32" s="59"/>
+      <c r="K32" s="59"/>
     </row>
     <row r="43" spans="9:9">
       <c r="I43" s="2" t="s">

--- a/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
+++ b/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
@@ -1,23 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\웹퍼블리셔과정_탐\github\WPC-626-TOM\001.일정관리\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D020DC-DF03-4AFD-9432-C3FF69A52584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21795" windowHeight="14595"/>
   </bookViews>
   <sheets>
     <sheet name="Hi-Media 반응형 웹퍼블리셔 1회차 주별 상세일정" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -147,10 +141,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>1차 레이아웃/상세코딩</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>0-1주차</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -171,10 +161,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>1차 상세코딩</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>도깨비 PJ 와이어프레이밍</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -188,10 +174,6 @@
   </si>
   <si>
     <t>보그 PJ 상세코딩</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>도깨비 PJ 상세코딩</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -472,39 +454,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>2차 상세코딩</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>2차 상세코딩</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>3차 주제선정 및 분석/설계</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>3차 PJ 상세코딩</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>3차 PJ 테스트/수정/배포</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>3차 PJ 발표 / 산출물작업</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>3차 산출물작업</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>1차 테스트/수정/배포
-2차 미니팀PJ 팀구성/주제선정</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>1차 주제선정 및 분석 / 설계</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -530,14 +479,58 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>도깨비 PJ 프로토타이핑 / 상세코딩</t>
+    <t>도깨비 PJ 프로토타이핑 준비</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>도깨비 PJ 프로토타이핑</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 제출 피드백 보완</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 제출 피드백 보완</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 프로토타이핑</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 상세코딩</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차 주제선정 및 분석/설계</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차 PJ 상세코딩</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차 PJ 테스트/수정/배포</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차 PJ 발표 / 산출물작업</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차 산출물작업</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>HTML5 + CSS3 응용연습</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="#\ &quot;일&quot;"/>
     <numFmt numFmtId="177" formatCode="&quot;총&quot;\ #\ &quot;일&quot;"/>
@@ -1047,6 +1040,15 @@
     <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1067,22 +1069,13 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="표준 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="표준 4" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="표준 2" xfId="2"/>
+    <cellStyle name="표준 3" xfId="3"/>
+    <cellStyle name="표준 4" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1140,7 +1133,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1173,26 +1166,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1225,23 +1201,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1417,12 +1376,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L43"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="1" max="1" width="2.375" customWidth="1"/>
     <col min="2" max="2" width="7.25" style="2" bestFit="1" customWidth="1"/>
@@ -1440,41 +1399,41 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" thickBot="1"/>
     <row r="2" spans="1:12" ht="53.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="60" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="62"/>
+      <c r="B2" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="65"/>
     </row>
     <row r="3" spans="1:12" ht="18.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="34.5" customHeight="1">
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
@@ -1482,7 +1441,7 @@
         <v>10</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>31</v>
@@ -1499,7 +1458,7 @@
     </row>
     <row r="5" spans="1:12" s="3" customFormat="1" ht="48" hidden="1" customHeight="1">
       <c r="B5" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" s="10">
         <v>45561</v>
@@ -1521,13 +1480,13 @@
       <c r="I5" s="11"/>
       <c r="J5" s="11"/>
       <c r="K5" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L5" s="15"/>
     </row>
     <row r="6" spans="1:12" s="3" customFormat="1" ht="48" hidden="1" customHeight="1">
       <c r="B6" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" s="10">
         <v>45565</v>
@@ -1549,13 +1508,13 @@
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
       <c r="K6" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L6" s="15"/>
     </row>
     <row r="7" spans="1:12" s="3" customFormat="1" ht="48" hidden="1" customHeight="1">
       <c r="B7" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="10">
         <v>45572</v>
@@ -1577,7 +1536,7 @@
       <c r="I7" s="11"/>
       <c r="J7" s="11"/>
       <c r="K7" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L7" s="15"/>
     </row>
@@ -1599,16 +1558,16 @@
         <v>2</v>
       </c>
       <c r="G8" s="44" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H8" s="42"/>
       <c r="I8" s="42"/>
       <c r="J8" s="42"/>
       <c r="K8" s="45" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L8" s="46" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
@@ -1629,17 +1588,17 @@
         <v>5</v>
       </c>
       <c r="G9" s="44" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H9" s="51"/>
       <c r="I9" s="49" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J9" s="49" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K9" s="52" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="L9" s="53"/>
     </row>
@@ -1661,17 +1620,17 @@
         <v>5</v>
       </c>
       <c r="G10" s="44" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H10" s="51"/>
       <c r="I10" s="49" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J10" s="49" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="K10" s="52" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="L10" s="53"/>
     </row>
@@ -1693,17 +1652,17 @@
         <v>5</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H11" s="55"/>
       <c r="I11" s="49" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J11" s="52" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="K11" s="52" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L11" s="53"/>
     </row>
@@ -1725,17 +1684,17 @@
         <v>5</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H12" s="51"/>
       <c r="I12" s="49" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J12" s="52" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="K12" s="52" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L12" s="53"/>
     </row>
@@ -1757,17 +1716,17 @@
         <v>2</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H13" s="51"/>
       <c r="I13" s="49" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J13" s="52" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K13" s="52" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="L13" s="53"/>
     </row>
@@ -1789,86 +1748,86 @@
         <v>5</v>
       </c>
       <c r="G14" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="H14" s="65" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="H14" s="58" t="s">
+        <v>54</v>
       </c>
       <c r="I14" s="52" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="J14" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="K14" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="K14" s="52" t="s">
-        <v>97</v>
-      </c>
       <c r="L14" s="46"/>
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="A15" s="34"/>
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="48">
         <v>45880</v>
       </c>
-      <c r="D15" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="36">
+      <c r="D15" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="48">
         <v>45883</v>
       </c>
-      <c r="F15" s="38">
+      <c r="F15" s="50">
         <f>DAYS360(C15,E15)+1</f>
         <v>4</v>
       </c>
-      <c r="G15" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="H15" s="63"/>
-      <c r="I15" s="39" t="s">
+      <c r="G15" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" s="51"/>
+      <c r="I15" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="J15" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="K15" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="J15" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="K15" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="L15" s="64"/>
+      <c r="L15" s="53"/>
     </row>
     <row r="16" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B16" s="17" t="s">
+      <c r="A16" s="34"/>
+      <c r="B16" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="36">
         <v>45887</v>
       </c>
-      <c r="D16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="18">
+      <c r="D16" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="36">
         <v>45891</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="38">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G16" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="H16" s="21"/>
-      <c r="I16" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="J16" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="K16" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="L16" s="23"/>
+      <c r="G16" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="56"/>
+      <c r="I16" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="J16" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="K16" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="L16" s="57"/>
     </row>
     <row r="17" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B17" s="17" t="s">
@@ -1888,22 +1847,22 @@
         <v>5</v>
       </c>
       <c r="G17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="H17" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="30" t="s">
-        <v>64</v>
-      </c>
       <c r="I17" s="22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J17" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K17" s="22" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L17" s="28" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
@@ -1924,17 +1883,17 @@
         <v>5</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H18" s="21"/>
       <c r="I18" s="22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="K18" s="22" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L18" s="23"/>
     </row>
@@ -1956,19 +1915,19 @@
         <v>5</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H19" s="30" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="K19" s="22" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L19" s="23"/>
     </row>
@@ -1990,19 +1949,19 @@
         <v>5</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H20" s="30" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="K20" s="22" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L20" s="23"/>
     </row>
@@ -2024,17 +1983,17 @@
         <v>5</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H21" s="21"/>
       <c r="I21" s="22" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J21" s="54" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="K21" s="22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L21" s="23"/>
     </row>
@@ -2056,17 +2015,17 @@
         <v>4</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H22" s="21"/>
       <c r="I22" s="22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="K22" s="22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L22" s="23"/>
     </row>
@@ -2088,17 +2047,17 @@
         <v>1</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H23" s="21"/>
       <c r="I23" s="22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="K23" s="22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L23" s="23"/>
     </row>
@@ -2120,19 +2079,19 @@
         <v>5</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H24" s="30" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I24" s="22" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="K24" s="22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L24" s="23"/>
     </row>
@@ -2154,19 +2113,19 @@
         <v>5</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H25" s="30" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I25" s="21" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="K25" s="22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L25" s="23"/>
     </row>
@@ -2188,22 +2147,22 @@
         <v>5</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H26" s="31" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I26" s="21" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="K26" s="22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L26" s="29" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="2:12" ht="56.45" customHeight="1">
@@ -2224,19 +2183,19 @@
         <v>5</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H27" s="30" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J27" s="19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K27" s="22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L27" s="25"/>
     </row>
@@ -2258,17 +2217,17 @@
         <v>5</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H28" s="26"/>
       <c r="I28" s="21" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J28" s="19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K28" s="22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L28" s="24"/>
     </row>
@@ -2290,22 +2249,22 @@
         <v>2</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H29" s="30" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I29" s="21" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J29" s="19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K29" s="22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L29" s="27" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="2:12" ht="47.25" customHeight="1" thickBot="1">
@@ -2317,36 +2276,36 @@
       </c>
     </row>
     <row r="31" spans="2:12" ht="21.75" customHeight="1">
-      <c r="B31" s="58" t="s">
+      <c r="B31" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="58"/>
-    </row>
-    <row r="32" spans="2:12" s="5" customFormat="1" ht="26.25">
-      <c r="B32" s="59" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" s="59"/>
-      <c r="D32" s="59"/>
-      <c r="E32" s="59"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="59"/>
-      <c r="I32" s="59"/>
-      <c r="J32" s="59"/>
-      <c r="K32" s="59"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="61"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="61"/>
+      <c r="K31" s="61"/>
+    </row>
+    <row r="32" spans="2:12" s="5" customFormat="1" ht="27">
+      <c r="B32" s="62" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="62"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="62"/>
+      <c r="G32" s="62"/>
+      <c r="H32" s="62"/>
+      <c r="I32" s="62"/>
+      <c r="J32" s="62"/>
+      <c r="K32" s="62"/>
     </row>
     <row r="43" spans="9:9">
       <c r="I43" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2364,9 +2323,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2374,9 +2333,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
+++ b/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
@@ -871,7 +871,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1038,12 +1038,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1397,43 +1391,43 @@
     <col min="12" max="12" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17.25" thickBot="1"/>
-    <row r="2" spans="1:12" ht="53.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="63" t="s">
+    <row r="1" spans="2:12" ht="17.25" thickBot="1"/>
+    <row r="2" spans="2:12" ht="53.25" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B2" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="65"/>
-    </row>
-    <row r="3" spans="1:12" ht="18.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="59"/>
-    </row>
-    <row r="4" spans="1:12" s="3" customFormat="1" ht="34.5" customHeight="1">
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="63"/>
+    </row>
+    <row r="3" spans="2:12" ht="18.75" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+    </row>
+    <row r="4" spans="2:12" s="3" customFormat="1" ht="34.5" customHeight="1">
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="60" t="s">
+      <c r="C4" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
@@ -1456,7 +1450,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="3" customFormat="1" ht="48" hidden="1" customHeight="1">
+    <row r="5" spans="2:12" s="3" customFormat="1" ht="48" hidden="1" customHeight="1">
       <c r="B5" s="9" t="s">
         <v>33</v>
       </c>
@@ -1484,7 +1478,7 @@
       </c>
       <c r="L5" s="15"/>
     </row>
-    <row r="6" spans="1:12" s="3" customFormat="1" ht="48" hidden="1" customHeight="1">
+    <row r="6" spans="2:12" s="3" customFormat="1" ht="48" hidden="1" customHeight="1">
       <c r="B6" s="9" t="s">
         <v>34</v>
       </c>
@@ -1512,7 +1506,7 @@
       </c>
       <c r="L6" s="15"/>
     </row>
-    <row r="7" spans="1:12" s="3" customFormat="1" ht="48" hidden="1" customHeight="1">
+    <row r="7" spans="2:12" s="3" customFormat="1" ht="48" hidden="1" customHeight="1">
       <c r="B7" s="9" t="s">
         <v>35</v>
       </c>
@@ -1540,7 +1534,7 @@
       </c>
       <c r="L7" s="15"/>
     </row>
-    <row r="8" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="8" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B8" s="40" t="s">
         <v>12</v>
       </c>
@@ -1570,7 +1564,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="9" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B9" s="47" t="s">
         <v>15</v>
       </c>
@@ -1602,7 +1596,7 @@
       </c>
       <c r="L9" s="53"/>
     </row>
-    <row r="10" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="10" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B10" s="47" t="s">
         <v>0</v>
       </c>
@@ -1634,7 +1628,7 @@
       </c>
       <c r="L10" s="53"/>
     </row>
-    <row r="11" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="11" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B11" s="47" t="s">
         <v>1</v>
       </c>
@@ -1666,7 +1660,7 @@
       </c>
       <c r="L11" s="53"/>
     </row>
-    <row r="12" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="12" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B12" s="47" t="s">
         <v>2</v>
       </c>
@@ -1698,7 +1692,7 @@
       </c>
       <c r="L12" s="53"/>
     </row>
-    <row r="13" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="13" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B13" s="47" t="s">
         <v>3</v>
       </c>
@@ -1730,7 +1724,7 @@
       </c>
       <c r="L13" s="53"/>
     </row>
-    <row r="14" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="14" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B14" s="47" t="s">
         <v>4</v>
       </c>
@@ -1750,7 +1744,7 @@
       <c r="G14" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="H14" s="58" t="s">
+      <c r="H14" s="56" t="s">
         <v>54</v>
       </c>
       <c r="I14" s="52" t="s">
@@ -1764,7 +1758,7 @@
       </c>
       <c r="L14" s="46"/>
     </row>
-    <row r="15" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="15" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B15" s="47" t="s">
         <v>5</v>
       </c>
@@ -1796,76 +1790,76 @@
       </c>
       <c r="L15" s="53"/>
     </row>
-    <row r="16" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="A16" s="34"/>
-      <c r="B16" s="35" t="s">
+    <row r="16" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+      <c r="B16" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="48">
         <v>45887</v>
       </c>
-      <c r="D16" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="36">
+      <c r="D16" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="48">
         <v>45891</v>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="50">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G16" s="33" t="s">
+      <c r="G16" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="56"/>
-      <c r="I16" s="39" t="s">
+      <c r="H16" s="51"/>
+      <c r="I16" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="J16" s="37" t="s">
+      <c r="J16" s="49" t="s">
         <v>106</v>
       </c>
-      <c r="K16" s="39" t="s">
+      <c r="K16" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="L16" s="57"/>
-    </row>
-    <row r="17" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B17" s="17" t="s">
+      <c r="L16" s="53"/>
+    </row>
+    <row r="17" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+      <c r="A17" s="34"/>
+      <c r="B17" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="36">
         <v>45894</v>
       </c>
-      <c r="D17" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="18">
+      <c r="D17" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="36">
         <v>45898</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="38">
         <f>DAYS360(C17,E17)+1</f>
         <v>5</v>
       </c>
-      <c r="G17" s="16" t="s">
+      <c r="G17" s="33" t="s">
         <v>58</v>
       </c>
       <c r="H17" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="I17" s="22" t="s">
+      <c r="I17" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="J17" s="54" t="s">
+      <c r="J17" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="K17" s="22" t="s">
+      <c r="K17" s="39" t="s">
         <v>85</v>
       </c>
       <c r="L17" s="28" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="18" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B18" s="17" t="s">
         <v>18</v>
       </c>
@@ -1897,7 +1891,7 @@
       </c>
       <c r="L18" s="23"/>
     </row>
-    <row r="19" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="19" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B19" s="17" t="s">
         <v>19</v>
       </c>
@@ -1931,7 +1925,7 @@
       </c>
       <c r="L19" s="23"/>
     </row>
-    <row r="20" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="20" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B20" s="17" t="s">
         <v>20</v>
       </c>
@@ -1965,7 +1959,7 @@
       </c>
       <c r="L20" s="23"/>
     </row>
-    <row r="21" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="21" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B21" s="17" t="s">
         <v>21</v>
       </c>
@@ -1997,7 +1991,7 @@
       </c>
       <c r="L21" s="23"/>
     </row>
-    <row r="22" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="22" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B22" s="17" t="s">
         <v>22</v>
       </c>
@@ -2029,7 +2023,7 @@
       </c>
       <c r="L22" s="23"/>
     </row>
-    <row r="23" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="23" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B23" s="17" t="s">
         <v>23</v>
       </c>
@@ -2061,7 +2055,7 @@
       </c>
       <c r="L23" s="23"/>
     </row>
-    <row r="24" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="24" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B24" s="17" t="s">
         <v>24</v>
       </c>
@@ -2095,7 +2089,7 @@
       </c>
       <c r="L24" s="23"/>
     </row>
-    <row r="25" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="25" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B25" s="17" t="s">
         <v>25</v>
       </c>
@@ -2129,7 +2123,7 @@
       </c>
       <c r="L25" s="23"/>
     </row>
-    <row r="26" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="26" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B26" s="17" t="s">
         <v>26</v>
       </c>
@@ -2165,7 +2159,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="2:12" ht="56.45" customHeight="1">
+    <row r="27" spans="1:12" ht="56.45" customHeight="1">
       <c r="B27" s="17" t="s">
         <v>27</v>
       </c>
@@ -2199,7 +2193,7 @@
       </c>
       <c r="L27" s="25"/>
     </row>
-    <row r="28" spans="2:12" ht="56.45" customHeight="1">
+    <row r="28" spans="1:12" ht="56.45" customHeight="1">
       <c r="B28" s="17" t="s">
         <v>28</v>
       </c>
@@ -2231,7 +2225,7 @@
       </c>
       <c r="L28" s="24"/>
     </row>
-    <row r="29" spans="2:12" ht="56.45" customHeight="1">
+    <row r="29" spans="1:12" ht="56.45" customHeight="1">
       <c r="B29" s="17" t="s">
         <v>29</v>
       </c>
@@ -2267,7 +2261,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="2:12" ht="47.25" customHeight="1" thickBot="1">
+    <row r="30" spans="1:12" ht="47.25" customHeight="1" thickBot="1">
       <c r="C30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="4">
@@ -2275,33 +2269,33 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="2:12" ht="21.75" customHeight="1">
-      <c r="B31" s="61" t="s">
+    <row r="31" spans="1:12" ht="21.75" customHeight="1">
+      <c r="B31" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="61"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="61"/>
-      <c r="K31" s="61"/>
-    </row>
-    <row r="32" spans="2:12" s="5" customFormat="1" ht="27">
-      <c r="B32" s="62" t="s">
+      <c r="C31" s="59"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="59"/>
+      <c r="K31" s="59"/>
+    </row>
+    <row r="32" spans="1:12" s="5" customFormat="1" ht="27">
+      <c r="B32" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="C32" s="62"/>
-      <c r="D32" s="62"/>
-      <c r="E32" s="62"/>
-      <c r="F32" s="62"/>
-      <c r="G32" s="62"/>
-      <c r="H32" s="62"/>
-      <c r="I32" s="62"/>
-      <c r="J32" s="62"/>
-      <c r="K32" s="62"/>
+      <c r="C32" s="60"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="60"/>
+      <c r="K32" s="60"/>
     </row>
     <row r="43" spans="9:9">
       <c r="I43" s="2" t="s">

--- a/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
+++ b/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
@@ -1,17 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\웹퍼블리셔과정_탐\github\WPC-626-TOM\001.일정관리\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA5E2C3-50B7-4B5D-AC0C-F547B728AB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21795" windowHeight="14595"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hi-Media 반응형 웹퍼블리셔 1회차 주별 상세일정" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="118">
   <si>
     <t>3주차</t>
   </si>
@@ -390,11 +396,6 @@
   </si>
   <si>
     <t>HTML5 + CSS3 응용연습
-Javascript 응용 / 제이쿼리 기본</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>HTML5 + CSS3 응용연습
 제이쿼리 응용</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -511,26 +512,44 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>2차 PJ 테스트/수정/배포</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>2차 PJ 발표 / 산출물작업</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>2차 산출물작업</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>HTML5 + CSS3 응용연습</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>도깨비 PJ 프로토타이핑 / 코딩</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차 PJ UI 디자인</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차 PJ 프로토타입</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>HTML5 + CSS3 응용연습
+Javascript 응용</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>HTML5 + CSS3 응용연습
+제이쿼리 기본</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 PJ 자체점검</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="#\ &quot;일&quot;"/>
     <numFmt numFmtId="177" formatCode="&quot;총&quot;\ #\ &quot;일&quot;"/>
@@ -1067,9 +1086,9 @@
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2" xfId="2"/>
-    <cellStyle name="표준 3" xfId="3"/>
-    <cellStyle name="표준 4" xfId="1"/>
+    <cellStyle name="표준 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="표준 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="표준 4" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1127,7 +1146,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1160,9 +1179,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1195,6 +1231,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1370,12 +1423,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L43"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="2.375" customWidth="1"/>
     <col min="2" max="2" width="7.25" style="2" bestFit="1" customWidth="1"/>
@@ -1589,10 +1642,10 @@
         <v>39</v>
       </c>
       <c r="J9" s="49" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K9" s="52" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L9" s="53"/>
     </row>
@@ -1621,10 +1674,10 @@
         <v>38</v>
       </c>
       <c r="J10" s="49" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K10" s="52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L10" s="53"/>
     </row>
@@ -1653,10 +1706,10 @@
         <v>38</v>
       </c>
       <c r="J11" s="52" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K11" s="52" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L11" s="53"/>
     </row>
@@ -1682,13 +1735,13 @@
       </c>
       <c r="H12" s="51"/>
       <c r="I12" s="49" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J12" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K12" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L12" s="53"/>
     </row>
@@ -1714,13 +1767,13 @@
       </c>
       <c r="H13" s="51"/>
       <c r="I13" s="49" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J13" s="52" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K13" s="52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L13" s="53"/>
     </row>
@@ -1748,13 +1801,13 @@
         <v>54</v>
       </c>
       <c r="I14" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J14" s="52" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K14" s="52" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L14" s="46"/>
     </row>
@@ -1780,13 +1833,13 @@
       </c>
       <c r="H15" s="51"/>
       <c r="I15" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J15" s="49" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K15" s="52" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="L15" s="53"/>
     </row>
@@ -1812,13 +1865,13 @@
       </c>
       <c r="H16" s="51"/>
       <c r="I16" s="52" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J16" s="49" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K16" s="52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L16" s="53"/>
     </row>
@@ -1847,10 +1900,10 @@
         <v>61</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="J17" s="39" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K17" s="39" t="s">
         <v>85</v>
@@ -1881,10 +1934,10 @@
       </c>
       <c r="H18" s="21"/>
       <c r="I18" s="22" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K18" s="22" t="s">
         <v>85</v>
@@ -1918,10 +1971,10 @@
         <v>42</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K19" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L19" s="23"/>
     </row>
@@ -1952,10 +2005,10 @@
         <v>40</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K20" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L20" s="23"/>
     </row>
@@ -1984,10 +2037,10 @@
         <v>43</v>
       </c>
       <c r="J21" s="54" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="K21" s="22" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="L21" s="23"/>
     </row>
@@ -2016,10 +2069,10 @@
         <v>41</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K22" s="22" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="L22" s="23"/>
     </row>
@@ -2048,10 +2101,10 @@
         <v>41</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K23" s="22" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="L23" s="23"/>
     </row>
@@ -2082,10 +2135,10 @@
         <v>44</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="K24" s="22" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="L24" s="23"/>
     </row>
@@ -2116,10 +2169,10 @@
         <v>45</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K25" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L25" s="23"/>
     </row>
@@ -2150,10 +2203,10 @@
         <v>45</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K26" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L26" s="29" t="s">
         <v>76</v>
@@ -2186,10 +2239,10 @@
         <v>46</v>
       </c>
       <c r="J27" s="19" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="K27" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L27" s="25"/>
     </row>
@@ -2218,10 +2271,10 @@
         <v>47</v>
       </c>
       <c r="J28" s="19" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="K28" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L28" s="24"/>
     </row>
@@ -2252,10 +2305,10 @@
         <v>47</v>
       </c>
       <c r="J29" s="19" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K29" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L29" s="27" t="s">
         <v>73</v>
@@ -2283,7 +2336,7 @@
       <c r="J31" s="59"/>
       <c r="K31" s="59"/>
     </row>
-    <row r="32" spans="1:12" s="5" customFormat="1" ht="27">
+    <row r="32" spans="1:12" s="5" customFormat="1" ht="26.25">
       <c r="B32" s="60" t="s">
         <v>83</v>
       </c>
@@ -2317,9 +2370,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2327,9 +2380,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
+++ b/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\웹퍼블리셔과정_탐\github\WPC-626-TOM\001.일정관리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA5E2C3-50B7-4B5D-AC0C-F547B728AB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2F727C-57EC-43AB-B065-5A8700C89DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hi-Media 반응형 웹퍼블리셔 1회차 주별 상세일정" sheetId="1" r:id="rId1"/>
@@ -890,7 +890,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -975,9 +975,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1081,6 +1078,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1446,41 +1449,41 @@
   <sheetData>
     <row r="1" spans="2:12" ht="17.25" thickBot="1"/>
     <row r="2" spans="2:12" ht="53.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="63"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="62"/>
     </row>
     <row r="3" spans="2:12" ht="18.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="2:12" s="3" customFormat="1" ht="34.5" customHeight="1">
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
@@ -1588,361 +1591,361 @@
       <c r="L7" s="15"/>
     </row>
     <row r="8" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="41">
+      <c r="C8" s="40">
         <v>45834</v>
       </c>
-      <c r="D8" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="41">
+      <c r="D8" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="40">
         <v>45835</v>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="42">
         <f>DAYS360(C8,E8)+1</f>
         <v>2</v>
       </c>
-      <c r="G8" s="44" t="s">
+      <c r="G8" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="45" t="s">
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="L8" s="46" t="s">
+      <c r="L8" s="45" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="9" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="48">
+      <c r="C9" s="47">
         <v>45838</v>
       </c>
-      <c r="D9" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="48">
+      <c r="D9" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="47">
         <v>45842</v>
       </c>
-      <c r="F9" s="50">
+      <c r="F9" s="49">
         <f t="shared" ref="F9:F27" si="0">DAYS360(C9,E9)+1</f>
         <v>5</v>
       </c>
-      <c r="G9" s="44" t="s">
+      <c r="G9" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="51"/>
-      <c r="I9" s="49" t="s">
+      <c r="H9" s="50"/>
+      <c r="I9" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="49" t="s">
+      <c r="J9" s="48" t="s">
         <v>88</v>
       </c>
-      <c r="K9" s="52" t="s">
+      <c r="K9" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="L9" s="53"/>
+      <c r="L9" s="52"/>
     </row>
     <row r="10" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="48">
+      <c r="C10" s="47">
         <v>45845</v>
       </c>
-      <c r="D10" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="48">
+      <c r="D10" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="47">
         <v>45849</v>
       </c>
-      <c r="F10" s="50">
+      <c r="F10" s="49">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G10" s="44" t="s">
+      <c r="G10" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="H10" s="51"/>
-      <c r="I10" s="49" t="s">
+      <c r="H10" s="50"/>
+      <c r="I10" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="J10" s="49" t="s">
+      <c r="J10" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="K10" s="52" t="s">
+      <c r="K10" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="L10" s="53"/>
+      <c r="L10" s="52"/>
     </row>
     <row r="11" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="48">
+      <c r="C11" s="47">
         <v>45852</v>
       </c>
-      <c r="D11" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="48">
+      <c r="D11" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="47">
         <v>45856</v>
       </c>
-      <c r="F11" s="50">
+      <c r="F11" s="49">
         <f>DAYS360(C11,E11)+1</f>
         <v>5</v>
       </c>
-      <c r="G11" s="44" t="s">
+      <c r="G11" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="H11" s="55"/>
-      <c r="I11" s="49" t="s">
+      <c r="H11" s="54"/>
+      <c r="I11" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="52" t="s">
+      <c r="J11" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="K11" s="52" t="s">
+      <c r="K11" s="51" t="s">
         <v>91</v>
       </c>
-      <c r="L11" s="53"/>
+      <c r="L11" s="52"/>
     </row>
     <row r="12" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B12" s="47" t="s">
+      <c r="B12" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="48">
+      <c r="C12" s="47">
         <v>45859</v>
       </c>
-      <c r="D12" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="48">
+      <c r="D12" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="47">
         <v>45863</v>
       </c>
-      <c r="F12" s="50">
+      <c r="F12" s="49">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G12" s="44" t="s">
+      <c r="G12" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="51"/>
-      <c r="I12" s="49" t="s">
+      <c r="H12" s="50"/>
+      <c r="I12" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="J12" s="52" t="s">
+      <c r="J12" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="K12" s="52" t="s">
+      <c r="K12" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="L12" s="53"/>
+      <c r="L12" s="52"/>
     </row>
     <row r="13" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B13" s="47" t="s">
+      <c r="B13" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="48">
+      <c r="C13" s="47">
         <v>45866</v>
       </c>
-      <c r="D13" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="48">
+      <c r="D13" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="47">
         <v>45867</v>
       </c>
-      <c r="F13" s="50">
+      <c r="F13" s="49">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G13" s="44" t="s">
+      <c r="G13" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="51"/>
-      <c r="I13" s="49" t="s">
+      <c r="H13" s="50"/>
+      <c r="I13" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="J13" s="52" t="s">
+      <c r="J13" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="K13" s="52" t="s">
+      <c r="K13" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="L13" s="53"/>
+      <c r="L13" s="52"/>
     </row>
     <row r="14" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B14" s="47" t="s">
+      <c r="B14" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="48">
+      <c r="C14" s="47">
         <v>45873</v>
       </c>
-      <c r="D14" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="48">
+      <c r="D14" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="47">
         <v>45877</v>
       </c>
-      <c r="F14" s="50">
+      <c r="F14" s="49">
         <f>DAYS360(C14,E14)+1</f>
         <v>5</v>
       </c>
-      <c r="G14" s="44" t="s">
+      <c r="G14" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="H14" s="56" t="s">
+      <c r="H14" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="I14" s="52" t="s">
+      <c r="I14" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="J14" s="52" t="s">
+      <c r="J14" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="K14" s="52" t="s">
+      <c r="K14" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="L14" s="46"/>
+      <c r="L14" s="45"/>
     </row>
     <row r="15" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="48">
+      <c r="C15" s="47">
         <v>45880</v>
       </c>
-      <c r="D15" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="48">
+      <c r="D15" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="47">
         <v>45883</v>
       </c>
-      <c r="F15" s="50">
+      <c r="F15" s="49">
         <f>DAYS360(C15,E15)+1</f>
         <v>4</v>
       </c>
-      <c r="G15" s="44" t="s">
+      <c r="G15" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="H15" s="51"/>
-      <c r="I15" s="52" t="s">
+      <c r="H15" s="50"/>
+      <c r="I15" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="J15" s="49" t="s">
+      <c r="J15" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="K15" s="52" t="s">
+      <c r="K15" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="L15" s="53"/>
+      <c r="L15" s="52"/>
     </row>
     <row r="16" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="48">
+      <c r="C16" s="47">
         <v>45887</v>
       </c>
-      <c r="D16" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="48">
+      <c r="D16" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="47">
         <v>45891</v>
       </c>
-      <c r="F16" s="50">
+      <c r="F16" s="49">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G16" s="44" t="s">
+      <c r="G16" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="51"/>
-      <c r="I16" s="52" t="s">
+      <c r="H16" s="50"/>
+      <c r="I16" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="J16" s="49" t="s">
+      <c r="J16" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="K16" s="52" t="s">
+      <c r="K16" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="L16" s="53"/>
+      <c r="L16" s="52"/>
     </row>
     <row r="17" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="A17" s="34"/>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="36">
+      <c r="C17" s="47">
         <v>45894</v>
       </c>
-      <c r="D17" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="36">
+      <c r="D17" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="47">
         <v>45898</v>
       </c>
-      <c r="F17" s="38">
+      <c r="F17" s="49">
         <f>DAYS360(C17,E17)+1</f>
         <v>5</v>
       </c>
-      <c r="G17" s="33" t="s">
+      <c r="G17" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="H17" s="30" t="s">
+      <c r="H17" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="I17" s="39" t="s">
+      <c r="I17" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="J17" s="39" t="s">
+      <c r="J17" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="K17" s="39" t="s">
+      <c r="K17" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="L17" s="28" t="s">
+      <c r="L17" s="45" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B18" s="17" t="s">
+      <c r="A18" s="33"/>
+      <c r="B18" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="35">
         <v>45901</v>
       </c>
-      <c r="D18" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="18">
+      <c r="D18" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="35">
         <v>45905</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="37">
         <f>DAYS360(C18,E18)+1</f>
         <v>5</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="H18" s="21"/>
-      <c r="I18" s="22" t="s">
+      <c r="H18" s="63"/>
+      <c r="I18" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="J18" s="22" t="s">
+      <c r="J18" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="K18" s="22" t="s">
+      <c r="K18" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="L18" s="23"/>
+      <c r="L18" s="64"/>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B19" s="17" t="s">
@@ -1964,7 +1967,7 @@
       <c r="G19" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H19" s="30" t="s">
+      <c r="H19" s="29" t="s">
         <v>62</v>
       </c>
       <c r="I19" s="22" t="s">
@@ -1998,7 +2001,7 @@
       <c r="G20" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="H20" s="30" t="s">
+      <c r="H20" s="29" t="s">
         <v>77</v>
       </c>
       <c r="I20" s="22" t="s">
@@ -2036,7 +2039,7 @@
       <c r="I21" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="J21" s="54" t="s">
+      <c r="J21" s="53" t="s">
         <v>117</v>
       </c>
       <c r="K21" s="22" t="s">
@@ -2057,7 +2060,7 @@
       <c r="E22" s="18">
         <v>45932</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="31">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -2089,7 +2092,7 @@
       <c r="E23" s="18">
         <v>45940</v>
       </c>
-      <c r="F23" s="32">
+      <c r="F23" s="31">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2128,7 +2131,7 @@
       <c r="G24" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="H24" s="30" t="s">
+      <c r="H24" s="29" t="s">
         <v>78</v>
       </c>
       <c r="I24" s="22" t="s">
@@ -2162,7 +2165,7 @@
       <c r="G25" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="H25" s="30" t="s">
+      <c r="H25" s="29" t="s">
         <v>79</v>
       </c>
       <c r="I25" s="21" t="s">
@@ -2196,7 +2199,7 @@
       <c r="G26" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="H26" s="31" t="s">
+      <c r="H26" s="30" t="s">
         <v>82</v>
       </c>
       <c r="I26" s="21" t="s">
@@ -2208,7 +2211,7 @@
       <c r="K26" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="L26" s="29" t="s">
+      <c r="L26" s="28" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2232,7 +2235,7 @@
       <c r="G27" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="H27" s="30" t="s">
+      <c r="H27" s="29" t="s">
         <v>80</v>
       </c>
       <c r="I27" s="21" t="s">
@@ -2291,14 +2294,14 @@
       <c r="E29" s="18">
         <v>45979</v>
       </c>
-      <c r="F29" s="32">
+      <c r="F29" s="31">
         <f>DAYS360(C29,E29)+1</f>
         <v>2</v>
       </c>
       <c r="G29" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="H29" s="30" t="s">
+      <c r="H29" s="29" t="s">
         <v>81</v>
       </c>
       <c r="I29" s="21" t="s">
@@ -2323,32 +2326,32 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="21.75" customHeight="1">
-      <c r="B31" s="59" t="s">
+      <c r="B31" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="59"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="59"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="59"/>
-      <c r="J31" s="59"/>
-      <c r="K31" s="59"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="58"/>
     </row>
     <row r="32" spans="1:12" s="5" customFormat="1" ht="26.25">
-      <c r="B32" s="60" t="s">
+      <c r="B32" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="C32" s="60"/>
-      <c r="D32" s="60"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="60"/>
-      <c r="G32" s="60"/>
-      <c r="H32" s="60"/>
-      <c r="I32" s="60"/>
-      <c r="J32" s="60"/>
-      <c r="K32" s="60"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="59"/>
+      <c r="H32" s="59"/>
+      <c r="I32" s="59"/>
+      <c r="J32" s="59"/>
+      <c r="K32" s="59"/>
     </row>
     <row r="43" spans="9:9">
       <c r="I43" s="2" t="s">

--- a/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
+++ b/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\웹퍼블리셔과정_탐\github\WPC-626-TOM\001.일정관리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2F727C-57EC-43AB-B065-5A8700C89DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803319A5-3317-49C6-A1F8-993A3A53D5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="117">
   <si>
     <t>3주차</t>
   </si>
@@ -180,10 +180,6 @@
   </si>
   <si>
     <t>보그 PJ 상세코딩</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>도깨비 PJ 상세코딩</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -520,10 +516,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>도깨비 PJ 프로토타이핑 / 코딩</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>2차 PJ UI 디자인</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -543,6 +535,10 @@
   </si>
   <si>
     <t>1차 PJ 자체점검</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>도깨비 PJ 목업 + 상세코딩</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1059,6 +1055,9 @@
     <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1080,11 +1079,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1449,41 +1445,41 @@
   <sheetData>
     <row r="1" spans="2:12" ht="17.25" thickBot="1"/>
     <row r="2" spans="2:12" ht="53.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="62"/>
+      <c r="B2" s="61" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="63"/>
     </row>
     <row r="3" spans="2:12" ht="18.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="2:12" s="3" customFormat="1" ht="34.5" customHeight="1">
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
@@ -1491,7 +1487,7 @@
         <v>10</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>31</v>
@@ -1608,16 +1604,16 @@
         <v>2</v>
       </c>
       <c r="G8" s="43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H8" s="41"/>
       <c r="I8" s="41"/>
       <c r="J8" s="41"/>
       <c r="K8" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L8" s="45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
@@ -1638,17 +1634,17 @@
         <v>5</v>
       </c>
       <c r="G9" s="43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H9" s="50"/>
       <c r="I9" s="48" t="s">
         <v>39</v>
       </c>
       <c r="J9" s="48" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K9" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L9" s="52"/>
     </row>
@@ -1670,17 +1666,17 @@
         <v>5</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H10" s="50"/>
       <c r="I10" s="48" t="s">
         <v>38</v>
       </c>
       <c r="J10" s="48" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K10" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L10" s="52"/>
     </row>
@@ -1702,17 +1698,17 @@
         <v>5</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H11" s="54"/>
       <c r="I11" s="48" t="s">
         <v>38</v>
       </c>
       <c r="J11" s="51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L11" s="52"/>
     </row>
@@ -1734,17 +1730,17 @@
         <v>5</v>
       </c>
       <c r="G12" s="43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H12" s="50"/>
       <c r="I12" s="48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J12" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K12" s="51" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L12" s="52"/>
     </row>
@@ -1766,17 +1762,17 @@
         <v>2</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H13" s="50"/>
       <c r="I13" s="48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L13" s="52"/>
     </row>
@@ -1798,19 +1794,19 @@
         <v>5</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H14" s="55" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I14" s="51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J14" s="51" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K14" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L14" s="45"/>
     </row>
@@ -1832,17 +1828,17 @@
         <v>4</v>
       </c>
       <c r="G15" s="43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H15" s="50"/>
       <c r="I15" s="51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J15" s="48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L15" s="52"/>
     </row>
@@ -1864,17 +1860,17 @@
         <v>5</v>
       </c>
       <c r="G16" s="43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H16" s="50"/>
       <c r="I16" s="51" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J16" s="48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K16" s="51" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L16" s="52"/>
     </row>
@@ -1896,90 +1892,90 @@
         <v>5</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H17" s="55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I17" s="51" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J17" s="51" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L17" s="45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="A18" s="33"/>
-      <c r="B18" s="34" t="s">
+      <c r="B18" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="47">
         <v>45901</v>
       </c>
-      <c r="D18" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="35">
+      <c r="D18" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="47">
         <v>45905</v>
       </c>
-      <c r="F18" s="37">
+      <c r="F18" s="49">
         <f>DAYS360(C18,E18)+1</f>
         <v>5</v>
       </c>
-      <c r="G18" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="H18" s="63"/>
-      <c r="I18" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="J18" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="K18" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="L18" s="64"/>
+      <c r="G18" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="H18" s="50"/>
+      <c r="I18" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="J18" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="K18" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="L18" s="52"/>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B19" s="17" t="s">
+      <c r="A19" s="33"/>
+      <c r="B19" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="35">
         <v>45908</v>
       </c>
-      <c r="D19" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="18">
+      <c r="D19" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="35">
         <v>45912</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="37">
         <f>DAYS360(C19,E19)+1</f>
         <v>5</v>
       </c>
-      <c r="G19" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="H19" s="29" t="s">
+      <c r="G19" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="I19" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="J19" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="K19" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="L19" s="23"/>
+      <c r="H19" s="64" t="s">
+        <v>61</v>
+      </c>
+      <c r="I19" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="J19" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K19" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="L19" s="56"/>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B20" s="17" t="s">
@@ -1999,19 +1995,19 @@
         <v>5</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H20" s="29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I20" s="22" t="s">
         <v>40</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K20" s="22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L20" s="23"/>
     </row>
@@ -2033,17 +2029,17 @@
         <v>5</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H21" s="21"/>
       <c r="I21" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J21" s="53" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K21" s="22" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="L21" s="23"/>
     </row>
@@ -2065,17 +2061,17 @@
         <v>4</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H22" s="21"/>
       <c r="I22" s="22" t="s">
         <v>41</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K22" s="22" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L22" s="23"/>
     </row>
@@ -2097,17 +2093,17 @@
         <v>1</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H23" s="21"/>
       <c r="I23" s="22" t="s">
         <v>41</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K23" s="22" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L23" s="23"/>
     </row>
@@ -2129,19 +2125,19 @@
         <v>5</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H24" s="29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I24" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J24" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="K24" s="22" t="s">
         <v>114</v>
-      </c>
-      <c r="K24" s="22" t="s">
-        <v>116</v>
       </c>
       <c r="L24" s="23"/>
     </row>
@@ -2163,19 +2159,19 @@
         <v>5</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H25" s="29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I25" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K25" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L25" s="23"/>
     </row>
@@ -2197,22 +2193,22 @@
         <v>5</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H26" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I26" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K26" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L26" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="56.45" customHeight="1">
@@ -2233,19 +2229,19 @@
         <v>5</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H27" s="29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J27" s="19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K27" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L27" s="25"/>
     </row>
@@ -2267,17 +2263,17 @@
         <v>5</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H28" s="26"/>
       <c r="I28" s="21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J28" s="19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K28" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L28" s="24"/>
     </row>
@@ -2299,22 +2295,22 @@
         <v>2</v>
       </c>
       <c r="G29" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H29" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="I29" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="J29" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="L29" s="27" t="s">
         <v>72</v>
-      </c>
-      <c r="H29" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="I29" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="J29" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="K29" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L29" s="27" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="47.25" customHeight="1" thickBot="1">
@@ -2326,32 +2322,32 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="21.75" customHeight="1">
-      <c r="B31" s="58" t="s">
+      <c r="B31" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="58"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="59"/>
+      <c r="K31" s="59"/>
     </row>
     <row r="32" spans="1:12" s="5" customFormat="1" ht="26.25">
-      <c r="B32" s="59" t="s">
-        <v>83</v>
-      </c>
-      <c r="C32" s="59"/>
-      <c r="D32" s="59"/>
-      <c r="E32" s="59"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="59"/>
-      <c r="I32" s="59"/>
-      <c r="J32" s="59"/>
-      <c r="K32" s="59"/>
+      <c r="B32" s="60" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="60"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="60"/>
+      <c r="K32" s="60"/>
     </row>
     <row r="43" spans="9:9">
       <c r="I43" s="2" t="s">

--- a/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
+++ b/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\웹퍼블리셔과정_탐\github\WPC-626-TOM\001.일정관리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803319A5-3317-49C6-A1F8-993A3A53D5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D34287-B49A-441A-AAD2-6C6396BDD257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="115">
   <si>
     <t>3주차</t>
   </si>
@@ -180,11 +180,6 @@
   </si>
   <si>
     <t>보그 PJ 상세코딩</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>도깨비 PJ 상세코딩
-보그 PJ 분석/설계</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -500,10 +495,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>2차 주제선정 및 분석/설계</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>2차 PJ 상세코딩</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -513,14 +504,6 @@
   </si>
   <si>
     <t>HTML5 + CSS3 응용연습</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>2차 PJ UI 디자인</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>2차 PJ 프로토타입</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -534,11 +517,21 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>1차 PJ 자체점검</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>도깨비 PJ 목업 + 상세코딩</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>보그 PJ 분석/설계 + 상세코딩</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 상세코딩
+2차 주제선정</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 상세코딩
+2차 PJ 디자인 &amp; 프로토타입</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -682,24 +675,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -722,6 +697,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFF33"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCECFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -886,7 +879,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -968,94 +961,79 @@
     <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1079,8 +1057,17 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1091,6 +1078,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFCCECFF"/>
+      <color rgb="FFFFCCFF"/>
+      <color rgb="FFCCFF33"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1445,41 +1439,41 @@
   <sheetData>
     <row r="1" spans="2:12" ht="17.25" thickBot="1"/>
     <row r="2" spans="2:12" ht="53.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="63"/>
+      <c r="B2" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="58"/>
     </row>
     <row r="3" spans="2:12" ht="18.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="2:12" s="3" customFormat="1" ht="34.5" customHeight="1">
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
@@ -1487,7 +1481,7 @@
         <v>10</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>31</v>
@@ -1587,429 +1581,429 @@
       <c r="L7" s="15"/>
     </row>
     <row r="8" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="35">
         <v>45834</v>
       </c>
-      <c r="D8" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="40">
+      <c r="D8" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="35">
         <v>45835</v>
       </c>
-      <c r="F8" s="42">
+      <c r="F8" s="37">
         <f>DAYS360(C8,E8)+1</f>
         <v>2</v>
       </c>
-      <c r="G8" s="43" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="44" t="s">
-        <v>83</v>
-      </c>
-      <c r="L8" s="45" t="s">
-        <v>73</v>
+      <c r="G8" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="L8" s="40" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="47">
+      <c r="C9" s="42">
         <v>45838</v>
       </c>
-      <c r="D9" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="47">
+      <c r="D9" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="42">
         <v>45842</v>
       </c>
-      <c r="F9" s="49">
+      <c r="F9" s="44">
         <f t="shared" ref="F9:F27" si="0">DAYS360(C9,E9)+1</f>
         <v>5</v>
       </c>
-      <c r="G9" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="H9" s="50"/>
-      <c r="I9" s="48" t="s">
+      <c r="G9" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="45"/>
+      <c r="I9" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="K9" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="L9" s="52"/>
+      <c r="J9" s="43" t="s">
+        <v>86</v>
+      </c>
+      <c r="K9" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="L9" s="47"/>
     </row>
     <row r="10" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="42">
         <v>45845</v>
       </c>
-      <c r="D10" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="47">
+      <c r="D10" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="42">
         <v>45849</v>
       </c>
-      <c r="F10" s="49">
+      <c r="F10" s="44">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G10" s="43" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="50"/>
-      <c r="I10" s="48" t="s">
+      <c r="G10" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="45"/>
+      <c r="I10" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="J10" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="K10" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="L10" s="52"/>
+      <c r="J10" s="43" t="s">
+        <v>85</v>
+      </c>
+      <c r="K10" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="L10" s="47"/>
     </row>
     <row r="11" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="47">
+      <c r="C11" s="42">
         <v>45852</v>
       </c>
-      <c r="D11" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="47">
+      <c r="D11" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="42">
         <v>45856</v>
       </c>
-      <c r="F11" s="49">
+      <c r="F11" s="44">
         <f>DAYS360(C11,E11)+1</f>
         <v>5</v>
       </c>
-      <c r="G11" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="H11" s="54"/>
-      <c r="I11" s="48" t="s">
+      <c r="G11" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="49"/>
+      <c r="I11" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="K11" s="51" t="s">
-        <v>90</v>
-      </c>
-      <c r="L11" s="52"/>
+      <c r="J11" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="K11" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="L11" s="47"/>
     </row>
     <row r="12" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="47">
+      <c r="C12" s="42">
         <v>45859</v>
       </c>
-      <c r="D12" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="47">
+      <c r="D12" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="42">
         <v>45863</v>
       </c>
-      <c r="F12" s="49">
+      <c r="F12" s="44">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G12" s="43" t="s">
-        <v>52</v>
-      </c>
-      <c r="H12" s="50"/>
-      <c r="I12" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="J12" s="51" t="s">
+      <c r="G12" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="45"/>
+      <c r="I12" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="K12" s="51" t="s">
-        <v>91</v>
-      </c>
-      <c r="L12" s="52"/>
+      <c r="J12" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="K12" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="47"/>
     </row>
     <row r="13" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="47">
+      <c r="C13" s="42">
         <v>45866</v>
       </c>
-      <c r="D13" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="47">
+      <c r="D13" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="42">
         <v>45867</v>
       </c>
-      <c r="F13" s="49">
+      <c r="F13" s="44">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G13" s="43" t="s">
-        <v>52</v>
-      </c>
-      <c r="H13" s="50"/>
-      <c r="I13" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="J13" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="K13" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="L13" s="52"/>
+      <c r="G13" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="45"/>
+      <c r="I13" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="J13" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="K13" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="L13" s="47"/>
     </row>
     <row r="14" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="42">
         <v>45873</v>
       </c>
-      <c r="D14" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="47">
+      <c r="D14" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="42">
         <v>45877</v>
       </c>
-      <c r="F14" s="49">
+      <c r="F14" s="44">
         <f>DAYS360(C14,E14)+1</f>
         <v>5</v>
       </c>
-      <c r="G14" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="H14" s="55" t="s">
+      <c r="G14" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="I14" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="J14" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="K14" s="51" t="s">
-        <v>92</v>
-      </c>
-      <c r="L14" s="45"/>
+      <c r="H14" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="J14" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="K14" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="L14" s="40"/>
     </row>
     <row r="15" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="47">
+      <c r="C15" s="42">
         <v>45880</v>
       </c>
-      <c r="D15" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="47">
+      <c r="D15" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="42">
         <v>45883</v>
       </c>
-      <c r="F15" s="49">
+      <c r="F15" s="44">
         <f>DAYS360(C15,E15)+1</f>
         <v>4</v>
       </c>
-      <c r="G15" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="H15" s="50"/>
-      <c r="I15" s="51" t="s">
-        <v>101</v>
-      </c>
-      <c r="J15" s="48" t="s">
-        <v>103</v>
-      </c>
-      <c r="K15" s="51" t="s">
-        <v>110</v>
-      </c>
-      <c r="L15" s="52"/>
+      <c r="G15" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="45"/>
+      <c r="I15" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="J15" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="K15" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="47"/>
     </row>
     <row r="16" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="47">
+      <c r="C16" s="42">
         <v>45887</v>
       </c>
-      <c r="D16" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="47">
+      <c r="D16" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="42">
         <v>45891</v>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="44">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G16" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="H16" s="50"/>
-      <c r="I16" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="J16" s="48" t="s">
-        <v>104</v>
-      </c>
-      <c r="K16" s="51" t="s">
-        <v>93</v>
-      </c>
-      <c r="L16" s="52"/>
+      <c r="G16" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" s="45"/>
+      <c r="I16" s="46" t="s">
+        <v>101</v>
+      </c>
+      <c r="J16" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="K16" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="L16" s="47"/>
     </row>
     <row r="17" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="47">
+      <c r="C17" s="42">
         <v>45894</v>
       </c>
-      <c r="D17" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="47">
+      <c r="D17" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="42">
         <v>45898</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="44">
         <f>DAYS360(C17,E17)+1</f>
         <v>5</v>
       </c>
-      <c r="G17" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H17" s="55" t="s">
-        <v>60</v>
-      </c>
-      <c r="I17" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="J17" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="K17" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="L17" s="45" t="s">
-        <v>74</v>
+      <c r="G17" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="I17" s="46" t="s">
+        <v>101</v>
+      </c>
+      <c r="J17" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="K17" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="L17" s="40" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="47">
+      <c r="C18" s="42">
         <v>45901</v>
       </c>
-      <c r="D18" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="47">
+      <c r="D18" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="42">
         <v>45905</v>
       </c>
-      <c r="F18" s="49">
+      <c r="F18" s="44">
         <f>DAYS360(C18,E18)+1</f>
         <v>5</v>
       </c>
-      <c r="G18" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="H18" s="50"/>
-      <c r="I18" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="J18" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="K18" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="L18" s="52"/>
+      <c r="G18" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18" s="45"/>
+      <c r="I18" s="46" t="s">
+        <v>101</v>
+      </c>
+      <c r="J18" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="K18" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="L18" s="47"/>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="A19" s="33"/>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="42">
         <v>45908</v>
       </c>
-      <c r="D19" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="35">
+      <c r="D19" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="42">
         <v>45912</v>
       </c>
-      <c r="F19" s="37">
+      <c r="F19" s="44">
         <f>DAYS360(C19,E19)+1</f>
         <v>5</v>
       </c>
-      <c r="G19" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="H19" s="64" t="s">
+      <c r="G19" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="I19" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="J19" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="K19" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="L19" s="56"/>
+      <c r="H19" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I19" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="J19" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="K19" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="L19" s="47"/>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B20" s="17" t="s">
+      <c r="A20" s="28"/>
+      <c r="B20" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="30">
         <v>45915</v>
       </c>
-      <c r="D20" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="18">
+      <c r="D20" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="30">
         <v>45919</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="32">
         <f>DAYS360(C20,E20)+1</f>
         <v>5</v>
       </c>
-      <c r="G20" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="H20" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="I20" s="22" t="s">
+      <c r="G20" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="I20" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="J20" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="K20" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="L20" s="23"/>
+      <c r="J20" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="K20" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="L20" s="51"/>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B21" s="17" t="s">
@@ -2029,17 +2023,17 @@
         <v>5</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H21" s="21"/>
       <c r="I21" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="J21" s="53" t="s">
-        <v>115</v>
+        <v>40</v>
+      </c>
+      <c r="J21" s="48" t="s">
+        <v>105</v>
       </c>
       <c r="K21" s="22" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="L21" s="23"/>
     </row>
@@ -2056,22 +2050,22 @@
       <c r="E22" s="18">
         <v>45932</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="62">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H22" s="21"/>
       <c r="I22" s="22" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K22" s="22" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="L22" s="23"/>
     </row>
@@ -2088,22 +2082,22 @@
       <c r="E23" s="18">
         <v>45940</v>
       </c>
-      <c r="F23" s="31">
+      <c r="F23" s="62">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H23" s="21"/>
       <c r="I23" s="22" t="s">
         <v>41</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K23" s="22" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="L23" s="23"/>
     </row>
@@ -2125,19 +2119,19 @@
         <v>5</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="H24" s="29" t="s">
-        <v>77</v>
+        <v>65</v>
+      </c>
+      <c r="H24" s="61" t="s">
+        <v>76</v>
       </c>
       <c r="I24" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K24" s="22" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="L24" s="23"/>
     </row>
@@ -2159,19 +2153,19 @@
         <v>5</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="H25" s="29" t="s">
-        <v>78</v>
+        <v>66</v>
+      </c>
+      <c r="H25" s="61" t="s">
+        <v>77</v>
       </c>
       <c r="I25" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="K25" s="22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L25" s="23"/>
     </row>
@@ -2193,22 +2187,22 @@
         <v>5</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="H26" s="30" t="s">
-        <v>81</v>
+        <v>67</v>
+      </c>
+      <c r="H26" s="59" t="s">
+        <v>80</v>
       </c>
       <c r="I26" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K26" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="L26" s="28" t="s">
-        <v>75</v>
+        <v>84</v>
+      </c>
+      <c r="L26" s="60" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="56.45" customHeight="1">
@@ -2229,19 +2223,19 @@
         <v>5</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="H27" s="29" t="s">
-        <v>79</v>
+        <v>68</v>
+      </c>
+      <c r="H27" s="61" t="s">
+        <v>78</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J27" s="19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K27" s="22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L27" s="25"/>
     </row>
@@ -2263,17 +2257,17 @@
         <v>5</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H28" s="26"/>
       <c r="I28" s="21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J28" s="19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K28" s="22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L28" s="24"/>
     </row>
@@ -2290,27 +2284,27 @@
       <c r="E29" s="18">
         <v>45979</v>
       </c>
-      <c r="F29" s="31">
+      <c r="F29" s="62">
         <f>DAYS360(C29,E29)+1</f>
         <v>2</v>
       </c>
       <c r="G29" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="H29" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="I29" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="J29" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="L29" s="60" t="s">
         <v>71</v>
-      </c>
-      <c r="H29" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="I29" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="J29" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="K29" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="L29" s="27" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="47.25" customHeight="1" thickBot="1">
@@ -2322,32 +2316,32 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="21.75" customHeight="1">
-      <c r="B31" s="59" t="s">
+      <c r="B31" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="59"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="59"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="59"/>
-      <c r="J31" s="59"/>
-      <c r="K31" s="59"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="54"/>
+      <c r="J31" s="54"/>
+      <c r="K31" s="54"/>
     </row>
     <row r="32" spans="1:12" s="5" customFormat="1" ht="26.25">
-      <c r="B32" s="60" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" s="60"/>
-      <c r="D32" s="60"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="60"/>
-      <c r="G32" s="60"/>
-      <c r="H32" s="60"/>
-      <c r="I32" s="60"/>
-      <c r="J32" s="60"/>
-      <c r="K32" s="60"/>
+      <c r="B32" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="55"/>
+      <c r="J32" s="55"/>
+      <c r="K32" s="55"/>
     </row>
     <row r="43" spans="9:9">
       <c r="I43" s="2" t="s">

--- a/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
+++ b/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\웹퍼블리셔과정_탐\github\WPC-626-TOM\001.일정관리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D34287-B49A-441A-AAD2-6C6396BDD257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7759708-4AFE-47A3-8F20-4CB346CC1964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="113">
   <si>
     <t>3주차</t>
   </si>
@@ -176,14 +176,6 @@
   </si>
   <si>
     <t>도깨비 PJ 상세코딩</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>보그 PJ 상세코딩</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>보그 PJ 상세코딩</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -508,11 +500,6 @@
   </si>
   <si>
     <t>HTML5 + CSS3 응용연습
-Javascript 응용</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>HTML5 + CSS3 응용연습
 제이쿼리 기본</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -532,6 +519,11 @@
   <si>
     <t>1차 상세코딩
 2차 PJ 디자인 &amp; 프로토타입</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>HTML5 + CSS3 응용연습
+Javascript 응용 / 제이쿼리 기본</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -648,7 +640,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -693,12 +685,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCCFF33"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -879,7 +865,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1024,9 +1010,6 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1036,6 +1019,18 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1057,17 +1052,11 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1439,41 +1428,41 @@
   <sheetData>
     <row r="1" spans="2:12" ht="17.25" thickBot="1"/>
     <row r="2" spans="2:12" ht="53.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="56" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="58"/>
+      <c r="B2" s="59" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="61"/>
     </row>
     <row r="3" spans="2:12" ht="18.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
     </row>
     <row r="4" spans="2:12" s="3" customFormat="1" ht="34.5" customHeight="1">
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
@@ -1481,7 +1470,7 @@
         <v>10</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>31</v>
@@ -1598,16 +1587,16 @@
         <v>2</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H8" s="36"/>
       <c r="I8" s="36"/>
       <c r="J8" s="36"/>
       <c r="K8" s="39" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L8" s="40" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
@@ -1628,17 +1617,17 @@
         <v>5</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H9" s="45"/>
       <c r="I9" s="43" t="s">
         <v>39</v>
       </c>
       <c r="J9" s="43" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K9" s="46" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L9" s="47"/>
     </row>
@@ -1660,17 +1649,17 @@
         <v>5</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H10" s="45"/>
       <c r="I10" s="43" t="s">
         <v>38</v>
       </c>
       <c r="J10" s="43" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K10" s="46" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L10" s="47"/>
     </row>
@@ -1692,17 +1681,17 @@
         <v>5</v>
       </c>
       <c r="G11" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="H11" s="49"/>
+        <v>48</v>
+      </c>
+      <c r="H11" s="48"/>
       <c r="I11" s="43" t="s">
         <v>38</v>
       </c>
       <c r="J11" s="46" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K11" s="46" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L11" s="47"/>
     </row>
@@ -1724,17 +1713,17 @@
         <v>5</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H12" s="45"/>
       <c r="I12" s="43" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J12" s="46" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K12" s="46" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L12" s="47"/>
     </row>
@@ -1756,17 +1745,17 @@
         <v>2</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H13" s="45"/>
       <c r="I13" s="43" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J13" s="46" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K13" s="46" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L13" s="47"/>
     </row>
@@ -1788,19 +1777,19 @@
         <v>5</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H14" s="50" t="s">
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>50</v>
       </c>
       <c r="I14" s="46" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J14" s="46" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K14" s="46" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L14" s="40"/>
     </row>
@@ -1822,17 +1811,17 @@
         <v>4</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H15" s="45"/>
       <c r="I15" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="J15" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="J15" s="43" t="s">
-        <v>102</v>
-      </c>
       <c r="K15" s="46" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="L15" s="47"/>
     </row>
@@ -1854,17 +1843,17 @@
         <v>5</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H16" s="45"/>
       <c r="I16" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="J16" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="J16" s="43" t="s">
-        <v>103</v>
-      </c>
       <c r="K16" s="46" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L16" s="47"/>
     </row>
@@ -1886,22 +1875,22 @@
         <v>5</v>
       </c>
       <c r="G17" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="H17" s="50" t="s">
-        <v>59</v>
+        <v>54</v>
+      </c>
+      <c r="H17" s="49" t="s">
+        <v>57</v>
       </c>
       <c r="I17" s="46" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J17" s="46" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K17" s="46" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L17" s="40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
@@ -1922,17 +1911,17 @@
         <v>5</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H18" s="45"/>
       <c r="I18" s="46" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J18" s="46" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K18" s="46" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L18" s="47"/>
     </row>
@@ -1954,88 +1943,88 @@
         <v>5</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="H19" s="50" t="s">
-        <v>60</v>
+        <v>59</v>
+      </c>
+      <c r="H19" s="49" t="s">
+        <v>58</v>
       </c>
       <c r="I19" s="46" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J19" s="46" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K19" s="46" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L19" s="47"/>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="A20" s="28"/>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="42">
         <v>45915</v>
       </c>
-      <c r="D20" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="30">
+      <c r="D20" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="42">
         <v>45919</v>
       </c>
-      <c r="F20" s="32">
+      <c r="F20" s="44">
         <f>DAYS360(C20,E20)+1</f>
         <v>5</v>
       </c>
-      <c r="G20" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="H20" s="61" t="s">
-        <v>75</v>
-      </c>
-      <c r="I20" s="33" t="s">
+      <c r="G20" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" s="63" t="s">
+        <v>73</v>
+      </c>
+      <c r="I20" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="J20" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="K20" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="L20" s="51"/>
+      <c r="J20" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="K20" s="46" t="s">
+        <v>81</v>
+      </c>
+      <c r="L20" s="47"/>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B21" s="17" t="s">
+      <c r="A21" s="28"/>
+      <c r="B21" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="30">
         <v>45922</v>
       </c>
-      <c r="D21" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="18">
+      <c r="D21" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="30">
         <v>45926</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="32">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G21" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="H21" s="21"/>
-      <c r="I21" s="22" t="s">
+      <c r="G21" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" s="62"/>
+      <c r="I21" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="J21" s="48" t="s">
-        <v>105</v>
-      </c>
-      <c r="K21" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="L21" s="23"/>
+      <c r="J21" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="K21" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="L21" s="50"/>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B22" s="17" t="s">
@@ -2050,22 +2039,22 @@
       <c r="E22" s="18">
         <v>45932</v>
       </c>
-      <c r="F22" s="62">
+      <c r="F22" s="54">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H22" s="21"/>
       <c r="I22" s="22" t="s">
-        <v>112</v>
+        <v>40</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K22" s="22" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L22" s="23"/>
     </row>
@@ -2082,22 +2071,22 @@
       <c r="E23" s="18">
         <v>45940</v>
       </c>
-      <c r="F23" s="62">
+      <c r="F23" s="54">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H23" s="21"/>
       <c r="I23" s="22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K23" s="22" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L23" s="23"/>
     </row>
@@ -2119,19 +2108,19 @@
         <v>5</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H24" s="61" t="s">
-        <v>76</v>
+        <v>63</v>
+      </c>
+      <c r="H24" s="53" t="s">
+        <v>74</v>
       </c>
       <c r="I24" s="22" t="s">
-        <v>42</v>
+        <v>109</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K24" s="22" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L24" s="23"/>
     </row>
@@ -2153,19 +2142,19 @@
         <v>5</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="H25" s="61" t="s">
-        <v>77</v>
+        <v>64</v>
+      </c>
+      <c r="H25" s="53" t="s">
+        <v>75</v>
       </c>
       <c r="I25" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K25" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L25" s="23"/>
     </row>
@@ -2187,22 +2176,22 @@
         <v>5</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="H26" s="59" t="s">
-        <v>80</v>
+        <v>65</v>
+      </c>
+      <c r="H26" s="51" t="s">
+        <v>78</v>
       </c>
       <c r="I26" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K26" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="L26" s="60" t="s">
-        <v>74</v>
+        <v>82</v>
+      </c>
+      <c r="L26" s="52" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="56.45" customHeight="1">
@@ -2223,19 +2212,19 @@
         <v>5</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="H27" s="61" t="s">
-        <v>78</v>
+        <v>66</v>
+      </c>
+      <c r="H27" s="53" t="s">
+        <v>76</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J27" s="19" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K27" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L27" s="25"/>
     </row>
@@ -2257,17 +2246,17 @@
         <v>5</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H28" s="26"/>
       <c r="I28" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J28" s="19" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K28" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L28" s="24"/>
     </row>
@@ -2284,27 +2273,27 @@
       <c r="E29" s="18">
         <v>45979</v>
       </c>
-      <c r="F29" s="62">
+      <c r="F29" s="54">
         <f>DAYS360(C29,E29)+1</f>
         <v>2</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="H29" s="61" t="s">
-        <v>79</v>
+        <v>68</v>
+      </c>
+      <c r="H29" s="53" t="s">
+        <v>77</v>
       </c>
       <c r="I29" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J29" s="19" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K29" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="L29" s="60" t="s">
-        <v>71</v>
+        <v>82</v>
+      </c>
+      <c r="L29" s="52" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="47.25" customHeight="1" thickBot="1">
@@ -2316,32 +2305,32 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="21.75" customHeight="1">
-      <c r="B31" s="54" t="s">
+      <c r="B31" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="54"/>
-      <c r="D31" s="54"/>
-      <c r="E31" s="54"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="54"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="54"/>
-      <c r="J31" s="54"/>
-      <c r="K31" s="54"/>
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
     </row>
     <row r="32" spans="1:12" s="5" customFormat="1" ht="26.25">
-      <c r="B32" s="55" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="55"/>
-      <c r="H32" s="55"/>
-      <c r="I32" s="55"/>
-      <c r="J32" s="55"/>
-      <c r="K32" s="55"/>
+      <c r="B32" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="58"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="58"/>
+      <c r="H32" s="58"/>
+      <c r="I32" s="58"/>
+      <c r="J32" s="58"/>
+      <c r="K32" s="58"/>
     </row>
     <row r="43" spans="9:9">
       <c r="I43" s="2" t="s">

--- a/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
+++ b/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\웹퍼블리셔과정_탐\github\WPC-626-TOM\001.일정관리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7759708-4AFE-47A3-8F20-4CB346CC1964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AEBD93F-C64A-4613-9B73-D2980526A466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1031,6 +1031,12 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1051,12 +1057,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1428,41 +1428,41 @@
   <sheetData>
     <row r="1" spans="2:12" ht="17.25" thickBot="1"/>
     <row r="2" spans="2:12" ht="53.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="63"/>
     </row>
     <row r="3" spans="2:12" ht="18.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="55"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="2:12" s="3" customFormat="1" ht="34.5" customHeight="1">
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
@@ -1979,7 +1979,7 @@
       <c r="G20" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="H20" s="63" t="s">
+      <c r="H20" s="56" t="s">
         <v>73</v>
       </c>
       <c r="I20" s="46" t="s">
@@ -1994,69 +1994,69 @@
       <c r="L20" s="47"/>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="A21" s="28"/>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="42">
         <v>45922</v>
       </c>
-      <c r="D21" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="30">
+      <c r="D21" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="42">
         <v>45926</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="44">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G21" s="27" t="s">
+      <c r="G21" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="H21" s="62"/>
-      <c r="I21" s="33" t="s">
+      <c r="H21" s="45"/>
+      <c r="I21" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="J21" s="33" t="s">
+      <c r="J21" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="K21" s="33" t="s">
+      <c r="K21" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="L21" s="50"/>
+      <c r="L21" s="47"/>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B22" s="17" t="s">
+      <c r="A22" s="28"/>
+      <c r="B22" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="18">
+      <c r="C22" s="30">
         <v>45929</v>
       </c>
-      <c r="D22" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="18">
+      <c r="D22" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="30">
         <v>45932</v>
       </c>
-      <c r="F22" s="54">
+      <c r="F22" s="32">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="H22" s="21"/>
-      <c r="I22" s="22" t="s">
+      <c r="H22" s="55"/>
+      <c r="I22" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="J22" s="22" t="s">
+      <c r="J22" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="K22" s="22" t="s">
+      <c r="K22" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="L22" s="23"/>
+      <c r="L22" s="50"/>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B23" s="17" t="s">
@@ -2305,32 +2305,32 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="21.75" customHeight="1">
-      <c r="B31" s="57" t="s">
+      <c r="B31" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="57"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="57"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="57"/>
-      <c r="K31" s="57"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="59"/>
+      <c r="K31" s="59"/>
     </row>
     <row r="32" spans="1:12" s="5" customFormat="1" ht="26.25">
-      <c r="B32" s="58" t="s">
+      <c r="B32" s="60" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="58"/>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="58"/>
-      <c r="H32" s="58"/>
-      <c r="I32" s="58"/>
-      <c r="J32" s="58"/>
-      <c r="K32" s="58"/>
+      <c r="C32" s="60"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="60"/>
+      <c r="K32" s="60"/>
     </row>
     <row r="43" spans="9:9">
       <c r="I43" s="2" t="s">

--- a/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
+++ b/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\웹퍼블리셔과정_탐\github\WPC-626-TOM\001.일정관리\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AEBD93F-C64A-4613-9B73-D2980526A466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21795" windowHeight="14595"/>
   </bookViews>
   <sheets>
     <sheet name="Hi-Media 반응형 웹퍼블리셔 1회차 주별 상세일정" sheetId="1" r:id="rId1"/>
@@ -530,7 +524,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="#\ &quot;일&quot;"/>
     <numFmt numFmtId="177" formatCode="&quot;총&quot;\ #\ &quot;일&quot;"/>
@@ -1061,9 +1055,9 @@
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="표준 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="표준 4" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="표준 2" xfId="2"/>
+    <cellStyle name="표준 3" xfId="3"/>
+    <cellStyle name="표준 4" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1128,7 +1122,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1161,26 +1155,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1213,23 +1190,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1405,12 +1365,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L43"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="1" max="1" width="2.375" customWidth="1"/>
     <col min="2" max="2" width="7.25" style="2" bestFit="1" customWidth="1"/>
@@ -2026,69 +1986,69 @@
       <c r="L21" s="47"/>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="A22" s="28"/>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="42">
         <v>45929</v>
       </c>
-      <c r="D22" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="30">
+      <c r="D22" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="42">
         <v>45932</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="44">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G22" s="27" t="s">
+      <c r="G22" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="H22" s="55"/>
-      <c r="I22" s="33" t="s">
+      <c r="H22" s="45"/>
+      <c r="I22" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="J22" s="33" t="s">
+      <c r="J22" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="K22" s="33" t="s">
+      <c r="K22" s="46" t="s">
         <v>107</v>
       </c>
-      <c r="L22" s="50"/>
+      <c r="L22" s="47"/>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B23" s="17" t="s">
+      <c r="A23" s="28"/>
+      <c r="B23" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="30">
         <v>45940</v>
       </c>
-      <c r="D23" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="18">
+      <c r="D23" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="30">
         <v>45940</v>
       </c>
-      <c r="F23" s="54">
+      <c r="F23" s="32">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G23" s="16" t="s">
+      <c r="G23" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="H23" s="21"/>
-      <c r="I23" s="22" t="s">
+      <c r="H23" s="55"/>
+      <c r="I23" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="J23" s="22" t="s">
+      <c r="J23" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="K23" s="22" t="s">
+      <c r="K23" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="L23" s="23"/>
+      <c r="L23" s="50"/>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B24" s="17" t="s">
@@ -2318,7 +2278,7 @@
       <c r="J31" s="59"/>
       <c r="K31" s="59"/>
     </row>
-    <row r="32" spans="1:12" s="5" customFormat="1" ht="26.25">
+    <row r="32" spans="1:12" s="5" customFormat="1" ht="27">
       <c r="B32" s="60" t="s">
         <v>79</v>
       </c>
@@ -2352,9 +2312,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2362,9 +2322,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
+++ b/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
@@ -1025,9 +1025,6 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1051,6 +1048,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1388,41 +1388,41 @@
   <sheetData>
     <row r="1" spans="2:12" ht="17.25" thickBot="1"/>
     <row r="2" spans="2:12" ht="53.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="63"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="62"/>
     </row>
     <row r="3" spans="2:12" ht="18.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="2:12" s="3" customFormat="1" ht="34.5" customHeight="1">
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
@@ -1939,7 +1939,7 @@
       <c r="G20" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="H20" s="56" t="s">
+      <c r="H20" s="55" t="s">
         <v>73</v>
       </c>
       <c r="I20" s="46" t="s">
@@ -2018,71 +2018,71 @@
       <c r="L22" s="47"/>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="A23" s="28"/>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="42">
         <v>45940</v>
       </c>
-      <c r="D23" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="30">
+      <c r="D23" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="42">
         <v>45940</v>
       </c>
-      <c r="F23" s="32">
+      <c r="F23" s="44">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G23" s="27" t="s">
+      <c r="G23" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="H23" s="55"/>
-      <c r="I23" s="33" t="s">
+      <c r="H23" s="45"/>
+      <c r="I23" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="J23" s="33" t="s">
+      <c r="J23" s="46" t="s">
         <v>110</v>
       </c>
-      <c r="K23" s="33" t="s">
+      <c r="K23" s="46" t="s">
         <v>107</v>
       </c>
-      <c r="L23" s="50"/>
+      <c r="L23" s="47"/>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B24" s="17" t="s">
+      <c r="A24" s="28"/>
+      <c r="B24" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="30">
         <v>45943</v>
       </c>
-      <c r="D24" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E24" s="18">
+      <c r="D24" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" s="30">
         <v>45947</v>
       </c>
-      <c r="F24" s="20">
+      <c r="F24" s="32">
         <f>DAYS360(C24,E24)+1</f>
         <v>5</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G24" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="H24" s="53" t="s">
+      <c r="H24" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="I24" s="22" t="s">
+      <c r="I24" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="J24" s="22" t="s">
+      <c r="J24" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="K24" s="22" t="s">
+      <c r="K24" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="L24" s="23"/>
+      <c r="L24" s="50"/>
     </row>
     <row r="25" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B25" s="17" t="s">
@@ -2265,32 +2265,32 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="21.75" customHeight="1">
-      <c r="B31" s="59" t="s">
+      <c r="B31" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="59"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="59"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="59"/>
-      <c r="J31" s="59"/>
-      <c r="K31" s="59"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="58"/>
     </row>
     <row r="32" spans="1:12" s="5" customFormat="1" ht="27">
-      <c r="B32" s="60" t="s">
+      <c r="B32" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="60"/>
-      <c r="D32" s="60"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="60"/>
-      <c r="G32" s="60"/>
-      <c r="H32" s="60"/>
-      <c r="I32" s="60"/>
-      <c r="J32" s="60"/>
-      <c r="K32" s="60"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="59"/>
+      <c r="H32" s="59"/>
+      <c r="I32" s="59"/>
+      <c r="J32" s="59"/>
+      <c r="K32" s="59"/>
     </row>
     <row r="43" spans="9:9">
       <c r="I43" s="2" t="s">

--- a/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
+++ b/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
@@ -859,7 +859,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -929,9 +929,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1049,8 +1046,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1388,41 +1385,41 @@
   <sheetData>
     <row r="1" spans="2:12" ht="17.25" thickBot="1"/>
     <row r="2" spans="2:12" ht="53.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="62"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="61"/>
     </row>
     <row r="3" spans="2:12" ht="18.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
     </row>
     <row r="4" spans="2:12" s="3" customFormat="1" ht="34.5" customHeight="1">
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
@@ -1530,593 +1527,593 @@
       <c r="L7" s="15"/>
     </row>
     <row r="8" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="34">
         <v>45834</v>
       </c>
-      <c r="D8" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="35">
+      <c r="D8" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="34">
         <v>45835</v>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="36">
         <f>DAYS360(C8,E8)+1</f>
         <v>2</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="39" t="s">
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="L8" s="40" t="s">
+      <c r="L8" s="39" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="42">
+      <c r="C9" s="41">
         <v>45838</v>
       </c>
-      <c r="D9" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="42">
+      <c r="D9" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="41">
         <v>45842</v>
       </c>
-      <c r="F9" s="44">
+      <c r="F9" s="43">
         <f t="shared" ref="F9:F27" si="0">DAYS360(C9,E9)+1</f>
         <v>5</v>
       </c>
-      <c r="G9" s="38" t="s">
+      <c r="G9" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="45"/>
-      <c r="I9" s="43" t="s">
+      <c r="H9" s="44"/>
+      <c r="I9" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="43" t="s">
+      <c r="J9" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="K9" s="46" t="s">
+      <c r="K9" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="L9" s="47"/>
+      <c r="L9" s="46"/>
     </row>
     <row r="10" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="42">
+      <c r="C10" s="41">
         <v>45845</v>
       </c>
-      <c r="D10" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="42">
+      <c r="D10" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="41">
         <v>45849</v>
       </c>
-      <c r="F10" s="44">
+      <c r="F10" s="43">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G10" s="38" t="s">
+      <c r="G10" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="H10" s="45"/>
-      <c r="I10" s="43" t="s">
+      <c r="H10" s="44"/>
+      <c r="I10" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="J10" s="43" t="s">
+      <c r="J10" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="K10" s="46" t="s">
+      <c r="K10" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="L10" s="47"/>
+      <c r="L10" s="46"/>
     </row>
     <row r="11" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="42">
+      <c r="C11" s="41">
         <v>45852</v>
       </c>
-      <c r="D11" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="42">
+      <c r="D11" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="41">
         <v>45856</v>
       </c>
-      <c r="F11" s="44">
+      <c r="F11" s="43">
         <f>DAYS360(C11,E11)+1</f>
         <v>5</v>
       </c>
-      <c r="G11" s="38" t="s">
+      <c r="G11" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="48"/>
-      <c r="I11" s="43" t="s">
+      <c r="H11" s="47"/>
+      <c r="I11" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="46" t="s">
+      <c r="J11" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="K11" s="46" t="s">
+      <c r="K11" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="L11" s="47"/>
+      <c r="L11" s="46"/>
     </row>
     <row r="12" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="41">
         <v>45859</v>
       </c>
-      <c r="D12" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="42">
+      <c r="D12" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="41">
         <v>45863</v>
       </c>
-      <c r="F12" s="44">
+      <c r="F12" s="43">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G12" s="38" t="s">
+      <c r="G12" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="H12" s="45"/>
-      <c r="I12" s="43" t="s">
+      <c r="H12" s="44"/>
+      <c r="I12" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="J12" s="46" t="s">
+      <c r="J12" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="K12" s="46" t="s">
+      <c r="K12" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="L12" s="47"/>
+      <c r="L12" s="46"/>
     </row>
     <row r="13" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="42">
+      <c r="C13" s="41">
         <v>45866</v>
       </c>
-      <c r="D13" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="42">
+      <c r="D13" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="41">
         <v>45867</v>
       </c>
-      <c r="F13" s="44">
+      <c r="F13" s="43">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G13" s="38" t="s">
+      <c r="G13" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="H13" s="45"/>
-      <c r="I13" s="43" t="s">
+      <c r="H13" s="44"/>
+      <c r="I13" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="J13" s="46" t="s">
+      <c r="J13" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="K13" s="46" t="s">
+      <c r="K13" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="L13" s="47"/>
+      <c r="L13" s="46"/>
     </row>
     <row r="14" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B14" s="41" t="s">
+      <c r="B14" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="42">
+      <c r="C14" s="41">
         <v>45873</v>
       </c>
-      <c r="D14" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="42">
+      <c r="D14" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="41">
         <v>45877</v>
       </c>
-      <c r="F14" s="44">
+      <c r="F14" s="43">
         <f>DAYS360(C14,E14)+1</f>
         <v>5</v>
       </c>
-      <c r="G14" s="38" t="s">
+      <c r="G14" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="H14" s="49" t="s">
+      <c r="H14" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="I14" s="46" t="s">
+      <c r="I14" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="J14" s="46" t="s">
+      <c r="J14" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="K14" s="46" t="s">
+      <c r="K14" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="L14" s="40"/>
+      <c r="L14" s="39"/>
     </row>
     <row r="15" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="42">
+      <c r="C15" s="41">
         <v>45880</v>
       </c>
-      <c r="D15" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="42">
+      <c r="D15" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="41">
         <v>45883</v>
       </c>
-      <c r="F15" s="44">
+      <c r="F15" s="43">
         <f>DAYS360(C15,E15)+1</f>
         <v>4</v>
       </c>
-      <c r="G15" s="38" t="s">
+      <c r="G15" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="H15" s="45"/>
-      <c r="I15" s="46" t="s">
+      <c r="H15" s="44"/>
+      <c r="I15" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="J15" s="43" t="s">
+      <c r="J15" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="K15" s="46" t="s">
+      <c r="K15" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="L15" s="47"/>
+      <c r="L15" s="46"/>
     </row>
     <row r="16" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="42">
+      <c r="C16" s="41">
         <v>45887</v>
       </c>
-      <c r="D16" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="42">
+      <c r="D16" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="41">
         <v>45891</v>
       </c>
-      <c r="F16" s="44">
+      <c r="F16" s="43">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G16" s="38" t="s">
+      <c r="G16" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="45"/>
-      <c r="I16" s="46" t="s">
+      <c r="H16" s="44"/>
+      <c r="I16" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="J16" s="43" t="s">
+      <c r="J16" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="K16" s="46" t="s">
+      <c r="K16" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="L16" s="47"/>
+      <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="42">
+      <c r="C17" s="41">
         <v>45894</v>
       </c>
-      <c r="D17" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="42">
+      <c r="D17" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="41">
         <v>45898</v>
       </c>
-      <c r="F17" s="44">
+      <c r="F17" s="43">
         <f>DAYS360(C17,E17)+1</f>
         <v>5</v>
       </c>
-      <c r="G17" s="38" t="s">
+      <c r="G17" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="H17" s="49" t="s">
+      <c r="H17" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="I17" s="46" t="s">
+      <c r="I17" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="J17" s="46" t="s">
+      <c r="J17" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="K17" s="46" t="s">
+      <c r="K17" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="L17" s="40" t="s">
+      <c r="L17" s="39" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="42">
+      <c r="C18" s="41">
         <v>45901</v>
       </c>
-      <c r="D18" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="42">
+      <c r="D18" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="41">
         <v>45905</v>
       </c>
-      <c r="F18" s="44">
+      <c r="F18" s="43">
         <f>DAYS360(C18,E18)+1</f>
         <v>5</v>
       </c>
-      <c r="G18" s="38" t="s">
+      <c r="G18" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="H18" s="45"/>
-      <c r="I18" s="46" t="s">
+      <c r="H18" s="44"/>
+      <c r="I18" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="J18" s="46" t="s">
+      <c r="J18" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="K18" s="46" t="s">
+      <c r="K18" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="L18" s="47"/>
+      <c r="L18" s="46"/>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="42">
+      <c r="C19" s="41">
         <v>45908</v>
       </c>
-      <c r="D19" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="42">
+      <c r="D19" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="41">
         <v>45912</v>
       </c>
-      <c r="F19" s="44">
+      <c r="F19" s="43">
         <f>DAYS360(C19,E19)+1</f>
         <v>5</v>
       </c>
-      <c r="G19" s="38" t="s">
+      <c r="G19" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="H19" s="49" t="s">
+      <c r="H19" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="I19" s="46" t="s">
+      <c r="I19" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="46" t="s">
+      <c r="J19" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="K19" s="46" t="s">
+      <c r="K19" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="L19" s="47"/>
+      <c r="L19" s="46"/>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="42">
+      <c r="C20" s="41">
         <v>45915</v>
       </c>
-      <c r="D20" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="42">
+      <c r="D20" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="41">
         <v>45919</v>
       </c>
-      <c r="F20" s="44">
+      <c r="F20" s="43">
         <f>DAYS360(C20,E20)+1</f>
         <v>5</v>
       </c>
-      <c r="G20" s="38" t="s">
+      <c r="G20" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="H20" s="55" t="s">
+      <c r="H20" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="I20" s="46" t="s">
+      <c r="I20" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="J20" s="46" t="s">
+      <c r="J20" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="K20" s="46" t="s">
+      <c r="K20" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="L20" s="47"/>
+      <c r="L20" s="46"/>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="42">
+      <c r="C21" s="41">
         <v>45922</v>
       </c>
-      <c r="D21" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="42">
+      <c r="D21" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="41">
         <v>45926</v>
       </c>
-      <c r="F21" s="44">
+      <c r="F21" s="43">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G21" s="38" t="s">
+      <c r="G21" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="H21" s="45"/>
-      <c r="I21" s="46" t="s">
+      <c r="H21" s="44"/>
+      <c r="I21" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="J21" s="46" t="s">
+      <c r="J21" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="K21" s="46" t="s">
+      <c r="K21" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="L21" s="47"/>
+      <c r="L21" s="46"/>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B22" s="41" t="s">
+      <c r="B22" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="42">
+      <c r="C22" s="41">
         <v>45929</v>
       </c>
-      <c r="D22" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="42">
+      <c r="D22" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="41">
         <v>45932</v>
       </c>
-      <c r="F22" s="44">
+      <c r="F22" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G22" s="38" t="s">
+      <c r="G22" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="H22" s="45"/>
-      <c r="I22" s="46" t="s">
+      <c r="H22" s="44"/>
+      <c r="I22" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="J22" s="46" t="s">
+      <c r="J22" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="K22" s="46" t="s">
+      <c r="K22" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="L22" s="47"/>
+      <c r="L22" s="46"/>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="42">
+      <c r="C23" s="41">
         <v>45940</v>
       </c>
-      <c r="D23" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="42">
+      <c r="D23" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="41">
         <v>45940</v>
       </c>
-      <c r="F23" s="44">
+      <c r="F23" s="43">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G23" s="38" t="s">
+      <c r="G23" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="H23" s="45"/>
-      <c r="I23" s="46" t="s">
+      <c r="H23" s="44"/>
+      <c r="I23" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="J23" s="46" t="s">
+      <c r="J23" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="K23" s="46" t="s">
+      <c r="K23" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="L23" s="47"/>
+      <c r="L23" s="46"/>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="A24" s="28"/>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="41">
         <v>45943</v>
       </c>
-      <c r="D24" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="E24" s="30">
+      <c r="D24" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" s="41">
         <v>45947</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="43">
         <f>DAYS360(C24,E24)+1</f>
         <v>5</v>
       </c>
-      <c r="G24" s="27" t="s">
+      <c r="G24" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="H24" s="63" t="s">
+      <c r="H24" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="I24" s="33" t="s">
+      <c r="I24" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="J24" s="33" t="s">
+      <c r="J24" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="K24" s="33" t="s">
+      <c r="K24" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="L24" s="50"/>
+      <c r="L24" s="46"/>
     </row>
     <row r="25" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B25" s="17" t="s">
+      <c r="A25" s="27"/>
+      <c r="B25" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="29">
         <v>45950</v>
       </c>
-      <c r="D25" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25" s="18">
+      <c r="D25" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="29">
         <v>45954</v>
       </c>
-      <c r="F25" s="20">
+      <c r="F25" s="31">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G25" s="16" t="s">
+      <c r="G25" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="H25" s="53" t="s">
+      <c r="H25" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="I25" s="21" t="s">
+      <c r="I25" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="J25" s="22" t="s">
+      <c r="J25" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="K25" s="22" t="s">
+      <c r="K25" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="L25" s="23"/>
+      <c r="L25" s="49"/>
     </row>
     <row r="26" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B26" s="17" t="s">
@@ -2138,7 +2135,7 @@
       <c r="G26" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H26" s="51" t="s">
+      <c r="H26" s="50" t="s">
         <v>78</v>
       </c>
       <c r="I26" s="21" t="s">
@@ -2150,7 +2147,7 @@
       <c r="K26" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="L26" s="52" t="s">
+      <c r="L26" s="51" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2174,7 +2171,7 @@
       <c r="G27" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="H27" s="53" t="s">
+      <c r="H27" s="52" t="s">
         <v>76</v>
       </c>
       <c r="I27" s="21" t="s">
@@ -2186,7 +2183,7 @@
       <c r="K27" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="L27" s="25"/>
+      <c r="L27" s="24"/>
     </row>
     <row r="28" spans="1:12" ht="56.45" customHeight="1">
       <c r="B28" s="17" t="s">
@@ -2208,7 +2205,7 @@
       <c r="G28" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="H28" s="26"/>
+      <c r="H28" s="25"/>
       <c r="I28" s="21" t="s">
         <v>43</v>
       </c>
@@ -2218,7 +2215,7 @@
       <c r="K28" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="L28" s="24"/>
+      <c r="L28" s="23"/>
     </row>
     <row r="29" spans="1:12" ht="56.45" customHeight="1">
       <c r="B29" s="17" t="s">
@@ -2233,14 +2230,14 @@
       <c r="E29" s="18">
         <v>45979</v>
       </c>
-      <c r="F29" s="54">
+      <c r="F29" s="53">
         <f>DAYS360(C29,E29)+1</f>
         <v>2</v>
       </c>
       <c r="G29" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="H29" s="53" t="s">
+      <c r="H29" s="52" t="s">
         <v>77</v>
       </c>
       <c r="I29" s="21" t="s">
@@ -2252,7 +2249,7 @@
       <c r="K29" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="L29" s="52" t="s">
+      <c r="L29" s="51" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2265,32 +2262,32 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="21.75" customHeight="1">
-      <c r="B31" s="58" t="s">
+      <c r="B31" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="58"/>
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
     </row>
     <row r="32" spans="1:12" s="5" customFormat="1" ht="27">
-      <c r="B32" s="59" t="s">
+      <c r="B32" s="58" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="59"/>
-      <c r="D32" s="59"/>
-      <c r="E32" s="59"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="59"/>
-      <c r="I32" s="59"/>
-      <c r="J32" s="59"/>
-      <c r="K32" s="59"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="58"/>
+      <c r="H32" s="58"/>
+      <c r="I32" s="58"/>
+      <c r="J32" s="58"/>
+      <c r="K32" s="58"/>
     </row>
     <row r="43" spans="9:9">
       <c r="I43" s="2" t="s">

--- a/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
+++ b/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="115">
   <si>
     <t>3주차</t>
   </si>
@@ -170,18 +170,6 @@
   </si>
   <si>
     <t>도깨비 PJ 상세코딩</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>보그 PJ 상세코딩</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>파일럿 PJ, DC PJ 분석/설계</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>DC PJ / 파일럿 PJ</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -502,10 +490,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>보그 PJ 분석/설계 + 상세코딩</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>1차 상세코딩
 2차 주제선정</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -518,6 +502,31 @@
   <si>
     <t>HTML5 + CSS3 응용연습
 Javascript 응용 / 제이쿼리 기본</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>산리오 PJ 상세코딩</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>쉐도잉 PJ 보완코딩</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>쉐도잉 PJ 차기작 준비</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>도깨비 PJ 상세코딩</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>쉐도잉 PJ 차기작 준비</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>보그 PJ 상세코딩
+산리오 PJ 분석/설계(금)</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -859,7 +868,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -932,9 +941,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1007,12 +1013,6 @@
     <xf numFmtId="14" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1046,7 +1046,19 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1385,41 +1397,41 @@
   <sheetData>
     <row r="1" spans="2:12" ht="17.25" thickBot="1"/>
     <row r="2" spans="2:12" ht="53.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="59" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="61"/>
+      <c r="B2" s="56" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="58"/>
     </row>
     <row r="3" spans="2:12" ht="18.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="55"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="2:12" s="3" customFormat="1" ht="34.5" customHeight="1">
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
@@ -1427,7 +1439,7 @@
         <v>10</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>31</v>
@@ -1527,663 +1539,663 @@
       <c r="L7" s="15"/>
     </row>
     <row r="8" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="33">
         <v>45834</v>
       </c>
-      <c r="D8" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="34">
+      <c r="D8" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="33">
         <v>45835</v>
       </c>
-      <c r="F8" s="36">
+      <c r="F8" s="35">
         <f>DAYS360(C8,E8)+1</f>
         <v>2</v>
       </c>
-      <c r="G8" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="L8" s="39" t="s">
-        <v>70</v>
+      <c r="G8" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="L8" s="38" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="41">
+      <c r="C9" s="40">
         <v>45838</v>
       </c>
-      <c r="D9" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="41">
+      <c r="D9" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="40">
         <v>45842</v>
       </c>
-      <c r="F9" s="43">
+      <c r="F9" s="42">
         <f t="shared" ref="F9:F27" si="0">DAYS360(C9,E9)+1</f>
         <v>5</v>
       </c>
-      <c r="G9" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="44"/>
-      <c r="I9" s="42" t="s">
+      <c r="G9" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="43"/>
+      <c r="I9" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="K9" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="L9" s="46"/>
+      <c r="J9" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="L9" s="45"/>
     </row>
     <row r="10" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="41">
+      <c r="C10" s="40">
         <v>45845</v>
       </c>
-      <c r="D10" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="41">
+      <c r="D10" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="40">
         <v>45849</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="42">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G10" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="44"/>
-      <c r="I10" s="42" t="s">
+      <c r="G10" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="43"/>
+      <c r="I10" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="J10" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="K10" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="L10" s="46"/>
+      <c r="J10" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="K10" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="L10" s="45"/>
     </row>
     <row r="11" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="41">
+      <c r="C11" s="40">
         <v>45852</v>
       </c>
-      <c r="D11" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="41">
+      <c r="D11" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="40">
         <v>45856</v>
       </c>
-      <c r="F11" s="43">
+      <c r="F11" s="42">
         <f>DAYS360(C11,E11)+1</f>
         <v>5</v>
       </c>
-      <c r="G11" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11" s="47"/>
-      <c r="I11" s="42" t="s">
+      <c r="G11" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="46"/>
+      <c r="I11" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="45" t="s">
-        <v>93</v>
-      </c>
-      <c r="K11" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="L11" s="46"/>
+      <c r="J11" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="K11" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="L11" s="45"/>
     </row>
     <row r="12" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="41">
+      <c r="C12" s="40">
         <v>45859</v>
       </c>
-      <c r="D12" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="41">
+      <c r="D12" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="40">
         <v>45863</v>
       </c>
-      <c r="F12" s="43">
+      <c r="F12" s="42">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G12" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="H12" s="44"/>
-      <c r="I12" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="J12" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="K12" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="L12" s="46"/>
+      <c r="G12" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="43"/>
+      <c r="I12" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="J12" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="K12" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="L12" s="45"/>
     </row>
     <row r="13" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="40">
         <v>45866</v>
       </c>
-      <c r="D13" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="41">
+      <c r="D13" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="40">
         <v>45867</v>
       </c>
-      <c r="F13" s="43">
+      <c r="F13" s="42">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G13" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="H13" s="44"/>
-      <c r="I13" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="J13" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="K13" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="L13" s="46"/>
+      <c r="G13" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="43"/>
+      <c r="I13" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="J13" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="K13" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="L13" s="45"/>
     </row>
     <row r="14" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="41">
+      <c r="C14" s="40">
         <v>45873</v>
       </c>
-      <c r="D14" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="41">
+      <c r="D14" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="40">
         <v>45877</v>
       </c>
-      <c r="F14" s="43">
+      <c r="F14" s="42">
         <f>DAYS360(C14,E14)+1</f>
         <v>5</v>
       </c>
-      <c r="G14" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="H14" s="48" t="s">
-        <v>50</v>
-      </c>
-      <c r="I14" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="J14" s="45" t="s">
+      <c r="G14" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="I14" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="J14" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="K14" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="L14" s="39"/>
+      <c r="L14" s="38"/>
     </row>
     <row r="15" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="41">
+      <c r="C15" s="40">
         <v>45880</v>
       </c>
-      <c r="D15" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="41">
+      <c r="D15" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="40">
         <v>45883</v>
       </c>
-      <c r="F15" s="43">
+      <c r="F15" s="42">
         <f>DAYS360(C15,E15)+1</f>
         <v>4</v>
       </c>
-      <c r="G15" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="H15" s="44"/>
-      <c r="I15" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="J15" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="K15" s="45" t="s">
-        <v>106</v>
-      </c>
-      <c r="L15" s="46"/>
+      <c r="G15" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15" s="43"/>
+      <c r="I15" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="J15" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="K15" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="L15" s="45"/>
     </row>
     <row r="16" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="40">
         <v>45887</v>
       </c>
-      <c r="D16" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="41">
+      <c r="D16" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="40">
         <v>45891</v>
       </c>
-      <c r="F16" s="43">
+      <c r="F16" s="42">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G16" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="H16" s="44"/>
-      <c r="I16" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="J16" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="K16" s="45" t="s">
-        <v>90</v>
-      </c>
-      <c r="L16" s="46"/>
+      <c r="G16" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="43"/>
+      <c r="I16" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="J16" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="K16" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="L16" s="45"/>
     </row>
     <row r="17" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="41">
+      <c r="C17" s="40">
         <v>45894</v>
       </c>
-      <c r="D17" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="41">
+      <c r="D17" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="40">
         <v>45898</v>
       </c>
-      <c r="F17" s="43">
+      <c r="F17" s="42">
         <f>DAYS360(C17,E17)+1</f>
         <v>5</v>
       </c>
-      <c r="G17" s="37" t="s">
+      <c r="G17" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="H17" s="48" t="s">
-        <v>57</v>
-      </c>
-      <c r="I17" s="45" t="s">
+      <c r="I17" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="J17" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="J17" s="45" t="s">
-        <v>102</v>
-      </c>
-      <c r="K17" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="L17" s="39" t="s">
-        <v>71</v>
+      <c r="K17" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="L17" s="38" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="40">
         <v>45901</v>
       </c>
-      <c r="D18" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="41">
+      <c r="D18" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="40">
         <v>45905</v>
       </c>
-      <c r="F18" s="43">
+      <c r="F18" s="42">
         <f>DAYS360(C18,E18)+1</f>
         <v>5</v>
       </c>
-      <c r="G18" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="H18" s="44"/>
-      <c r="I18" s="45" t="s">
+      <c r="G18" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" s="43"/>
+      <c r="I18" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="J18" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="J18" s="45" t="s">
-        <v>102</v>
-      </c>
-      <c r="K18" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="L18" s="46"/>
+      <c r="K18" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="L18" s="45"/>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="41">
+      <c r="C19" s="40">
         <v>45908</v>
       </c>
-      <c r="D19" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="41">
+      <c r="D19" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="40">
         <v>45912</v>
       </c>
-      <c r="F19" s="43">
+      <c r="F19" s="42">
         <f>DAYS360(C19,E19)+1</f>
         <v>5</v>
       </c>
-      <c r="G19" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="H19" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="I19" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="J19" s="45" t="s">
-        <v>103</v>
-      </c>
-      <c r="K19" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="L19" s="46"/>
+      <c r="G19" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="I19" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="J19" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="K19" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="L19" s="45"/>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="41">
+      <c r="C20" s="40">
         <v>45915</v>
       </c>
-      <c r="D20" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="41">
+      <c r="D20" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="40">
         <v>45919</v>
       </c>
-      <c r="F20" s="43">
+      <c r="F20" s="42">
         <f>DAYS360(C20,E20)+1</f>
         <v>5</v>
       </c>
-      <c r="G20" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="H20" s="54" t="s">
-        <v>73</v>
-      </c>
-      <c r="I20" s="45" t="s">
+      <c r="G20" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="H20" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="I20" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="J20" s="45" t="s">
-        <v>103</v>
-      </c>
-      <c r="K20" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="L20" s="46"/>
+      <c r="J20" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="K20" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="L20" s="45"/>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="41">
+      <c r="C21" s="40">
         <v>45922</v>
       </c>
-      <c r="D21" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="41">
+      <c r="D21" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="40">
         <v>45926</v>
       </c>
-      <c r="F21" s="43">
+      <c r="F21" s="42">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G21" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="H21" s="44"/>
-      <c r="I21" s="45" t="s">
+      <c r="G21" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="H21" s="43"/>
+      <c r="I21" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="J21" s="45" t="s">
-        <v>103</v>
-      </c>
-      <c r="K21" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="L21" s="46"/>
+      <c r="J21" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="K21" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="L21" s="45"/>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B22" s="40" t="s">
+      <c r="B22" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="41">
+      <c r="C22" s="40">
         <v>45929</v>
       </c>
-      <c r="D22" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="41">
+      <c r="D22" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="40">
         <v>45932</v>
       </c>
-      <c r="F22" s="43">
+      <c r="F22" s="42">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G22" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="H22" s="44"/>
-      <c r="I22" s="45" t="s">
+      <c r="G22" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22" s="43"/>
+      <c r="I22" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="J22" s="45" t="s">
-        <v>103</v>
-      </c>
-      <c r="K22" s="45" t="s">
-        <v>107</v>
-      </c>
-      <c r="L22" s="46"/>
+      <c r="J22" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="K22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L22" s="45"/>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B23" s="40" t="s">
+      <c r="B23" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="41">
+      <c r="C23" s="40">
         <v>45940</v>
       </c>
-      <c r="D23" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="41">
+      <c r="D23" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="40">
         <v>45940</v>
       </c>
-      <c r="F23" s="43">
+      <c r="F23" s="42">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G23" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="H23" s="44"/>
-      <c r="I23" s="45" t="s">
-        <v>40</v>
-      </c>
-      <c r="J23" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="K23" s="45" t="s">
-        <v>107</v>
-      </c>
-      <c r="L23" s="46"/>
+      <c r="G23" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="H23" s="43"/>
+      <c r="I23" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="J23" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="K23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L23" s="45"/>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="41">
+      <c r="C24" s="40">
         <v>45943</v>
       </c>
-      <c r="D24" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E24" s="41">
+      <c r="D24" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" s="40">
         <v>45947</v>
       </c>
-      <c r="F24" s="43">
+      <c r="F24" s="42">
         <f>DAYS360(C24,E24)+1</f>
         <v>5</v>
       </c>
-      <c r="G24" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="H24" s="54" t="s">
-        <v>74</v>
-      </c>
-      <c r="I24" s="45" t="s">
-        <v>109</v>
-      </c>
-      <c r="J24" s="45" t="s">
-        <v>111</v>
-      </c>
-      <c r="K24" s="45" t="s">
+      <c r="G24" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="H24" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="I24" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="J24" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="L24" s="46"/>
+      <c r="K24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L24" s="45"/>
     </row>
     <row r="25" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="A25" s="27"/>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="40">
         <v>45950</v>
       </c>
-      <c r="D25" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25" s="29">
+      <c r="D25" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="40">
         <v>45954</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="42">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G25" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H25" s="52" t="s">
-        <v>75</v>
-      </c>
-      <c r="I25" s="62" t="s">
-        <v>41</v>
-      </c>
-      <c r="J25" s="32" t="s">
-        <v>111</v>
-      </c>
-      <c r="K25" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="L25" s="49"/>
+      <c r="G25" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="H25" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="I25" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="J25" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="K25" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="L25" s="45"/>
     </row>
     <row r="26" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="18">
+      <c r="C26" s="40">
         <v>45957</v>
       </c>
-      <c r="D26" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E26" s="18">
+      <c r="D26" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="40">
         <v>45961</v>
       </c>
-      <c r="F26" s="20">
+      <c r="F26" s="42">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G26" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H26" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="I26" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="J26" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="K26" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="L26" s="51" t="s">
-        <v>72</v>
+      <c r="G26" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="H26" s="59" t="s">
+        <v>75</v>
+      </c>
+      <c r="I26" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="J26" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="K26" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="L26" s="60" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="56.45" customHeight="1">
-      <c r="B27" s="17" t="s">
+      <c r="A27" s="26"/>
+      <c r="B27" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="28">
         <v>45964</v>
       </c>
-      <c r="D27" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27" s="18">
+      <c r="D27" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="28">
         <v>45968</v>
       </c>
-      <c r="F27" s="20">
+      <c r="F27" s="30">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G27" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="H27" s="52" t="s">
-        <v>76</v>
-      </c>
-      <c r="I27" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="J27" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="K27" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="L27" s="24"/>
+      <c r="G27" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="H27" s="61" t="s">
+        <v>73</v>
+      </c>
+      <c r="I27" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="J27" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="K27" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="L27" s="63"/>
     </row>
     <row r="28" spans="1:12" ht="56.45" customHeight="1">
       <c r="B28" s="17" t="s">
@@ -2203,17 +2215,17 @@
         <v>5</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="H28" s="25"/>
+        <v>64</v>
+      </c>
+      <c r="H28" s="24"/>
       <c r="I28" s="21" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="J28" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K28" s="22" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L28" s="23"/>
     </row>
@@ -2230,27 +2242,27 @@
       <c r="E29" s="18">
         <v>45979</v>
       </c>
-      <c r="F29" s="53">
+      <c r="F29" s="50">
         <f>DAYS360(C29,E29)+1</f>
         <v>2</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="H29" s="52" t="s">
-        <v>77</v>
+        <v>65</v>
+      </c>
+      <c r="H29" s="49" t="s">
+        <v>74</v>
       </c>
       <c r="I29" s="21" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="J29" s="19" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K29" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="L29" s="51" t="s">
-        <v>69</v>
+        <v>79</v>
+      </c>
+      <c r="L29" s="48" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="47.25" customHeight="1" thickBot="1">
@@ -2262,32 +2274,32 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="21.75" customHeight="1">
-      <c r="B31" s="57" t="s">
+      <c r="B31" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="57"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="57"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="57"/>
-      <c r="K31" s="57"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="54"/>
+      <c r="J31" s="54"/>
+      <c r="K31" s="54"/>
     </row>
     <row r="32" spans="1:12" s="5" customFormat="1" ht="27">
-      <c r="B32" s="58" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" s="58"/>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="58"/>
-      <c r="H32" s="58"/>
-      <c r="I32" s="58"/>
-      <c r="J32" s="58"/>
-      <c r="K32" s="58"/>
+      <c r="B32" s="55" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="55"/>
+      <c r="J32" s="55"/>
+      <c r="K32" s="55"/>
     </row>
     <row r="43" spans="9:9">
       <c r="I43" s="2" t="s">

--- a/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
+++ b/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
@@ -23,11 +23,85 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="109">
   <x:si>
+    <x:t>프로토타입 기초데이터수집 및 스케치
+프로토타입 제작 및 사용성 테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1차 분석 / 설계
+포토샵 화면 디자인 작업
+2차 제출(8/8:금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비주얼 아이데이션 구상
+비주얼 아이데이션 전개
+시안 디자인 개발 심화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>디자인 구성요소 응용
+시각디자인 리서치 조사
+시각디자인 리서치 분석</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTML5 + CSS3 기본 및 응용연습
+그래픽 기초(일러스트) + (웹사이트 디자인)
+프로토타이핑(Figma)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>※ 휴강일: 7/30~8/1(휴가:3일), 8/15(광복절), 10/3(개천절), 10/6~10/9(추석:4일)</x:t>
+  </x:si>
+  <x:si>
     <x:t>____________________________________________________________________________________________________________________</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도깨비 PJ 와이어프레이밍</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도깨비 PJ UI 디자인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도깨비 PJ 프로토타이핑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스마트문화앱 UX 설계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10/27(월)
+작품발표회</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1차 제출 피드백 보완</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1차 상세코딩
+2차 주제선정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쉐도잉 PJ 차기작 준비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스마트문화앱 UI 디자인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11/18(화)
+수료식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작품발표회
+(10/27)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTML5 + CSS3 응용연습
+그래픽 응용(웹사이트 디자인)
+프로토타이핑(Figma)</x:t>
   </x:si>
   <x:si>
     <x:t>HTML5 + CSS3 응용연습
 Javascript 응용 / 제이쿼리 기본</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1차 분석 / UI디자인
+포토샵 화면 디자인 작업
+와이어프레이밍 제출(수)</x:t>
   </x:si>
   <x:si>
     <x:t>1차 분석 / UI디자인
@@ -35,13 +109,9 @@
 1차 제출(7/29:화)</x:t>
   </x:si>
   <x:si>
-    <x:t>1차 분석 / UI디자인
-포토샵 화면 디자인 작업
-와이어프레이밍 제출(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>개발환경셋팅: VS Code + Server + GitHub
-그래픽 기초(포토샵) + HTML 기초 + CSS 기초</x:t>
+    <x:t>HTML5 + CSS3 기초연습
+그래픽 기초(일러스트) + (웹사이트 디자인)
+프로토타이핑(Figma)</x:t>
   </x:si>
   <x:si>
     <x:t>HTML5 + CSS3 기초연습
@@ -50,58 +120,48 @@
   </x:si>
   <x:si>
     <x:t>HTML5 + CSS3 기초연습
-그래픽 기초(일러스트) + (웹사이트 디자인)
-프로토타이핑(Figma)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTML5 + CSS3 기초연습
 그래픽 기초(포토샵)
 와이어프레이밍(Balsamiq)</x:t>
   </x:si>
   <x:si>
-    <x:t>2주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>~</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>단위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5주차</x:t>
+    <x:t>(디지털디자인)UIUX 반응형 웹디자인 &amp; 웹퍼블리셔(디자인&amp;코딩) 양성 C 1회차 주별 상세일정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도깨비 PJ 상세코딩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2차 PJ 상세코딩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6/26(목)
+입학식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>디지털디자인 사후관리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로그래밍 언어 응용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCS 학습단위</x:t>
+  </x:si>
+  <x:si>
+    <x:t>디자인 구성요소 제작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>디자인 구성요소 설계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2차 산출물작업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>디자인 구성요소 응용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1차 프로토타이핑</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 쉐도잉 프로젝트</x:t>
   </x:si>
   <x:si>
     <x:t>산리오 PJ 상세코딩</x:t>
@@ -110,40 +170,12 @@
     <x:t>쉐도잉 PJ 보완코딩</x:t>
   </x:si>
   <x:si>
-    <x:t>HTML5 + CSS3 응용연습
-그래픽 응용(웹사이트 디자인)
-프로토타이핑(Figma)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비주얼 아이데이션 구상
-비주얼 아이데이션 전개
-시안 디자인 개발 심화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로토타입 기초데이터수집 및 스케치
-프로토타입 제작 및 사용성 테스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>디자인 구성요소 응용
-시각디자인 리서치 조사
-시각디자인 리서치 분석</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1차 분석 / 설계
-포토샵 화면 디자인 작업
-2차 제출(8/8:금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>※ 휴강일: 7/30~8/1(휴가:3일), 8/15(광복절), 10/3(개천절), 10/6~10/9(추석:4일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTML5 + CSS3 기본 및 응용연습
-그래픽 기초(일러스트) + (웹사이트 디자인)
-프로토타이핑(Figma)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서비스ㆍ경험디자인 관찰조사
-서비스ㆍ경험디자인 시나리오개발</x:t>
+    <x:t>개발환경셋팅: VS Code + Server + GitHub
+그래픽 기초(포토샵) + HTML 기초 + CSS 기초</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도깨비 PJ UI 디자인
+과목평가제출주간(금요일까지)</x:t>
   </x:si>
   <x:si>
     <x:t>디자인 리서치 및 
@@ -155,33 +187,64 @@
 개발 평가(9/9)</x:t>
   </x:si>
   <x:si>
+    <x:t>HTML5 + CSS3 응용연습
+Javascript 기본</x:t>
+  </x:si>
+  <x:si>
     <x:t>프로토타입 제작 및 사용성 테스트
 프로젝트 완료 최종보고</x:t>
   </x:si>
   <x:si>
-    <x:t>HTML5 + CSS3 응용연습
-Javascript 기본</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도깨비 PJ UI 디자인
-과목평가제출주간(금요일까지)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UI/UX 구성요소 설계 및 제작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTML5 + CSS3 응용연습</x:t>
-  </x:si>
-  <x:si>
-    <x:t>웹기초 + UI/UX개념 + 피그마</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사용자 리서치
-평가(9/16)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로토타입 제작
-평가(11/5)</x:t>
+    <x:t>서비스ㆍ경험디자인 관찰조사
+서비스ㆍ경험디자인 시나리오개발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>~</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>,</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도깨비 PJ 프로토타이핑 준비</x:t>
   </x:si>
   <x:si>
     <x:t>8/27(수)
@@ -189,94 +252,43 @@
 취업특강</x:t>
   </x:si>
   <x:si>
+    <x:t>프로토타입 제작
+평가(11/5)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UI/UX 구성요소 설계 및 제작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTML5 + CSS3 응용연습</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도깨비 PJ 목업 + 상세코딩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1차 주제선정 및 분석 / 설계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>웹기초 + UI/UX개념 + 피그마</x:t>
+  </x:si>
+  <x:si>
     <x:t>프로젝트 완료
 평가(11/17)</x:t>
   </x:si>
   <x:si>
-    <x:t>1차 주제선정 및 분석 / 설계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도깨비 PJ 목업 + 상세코딩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도깨비 PJ 프로토타이핑 준비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도깨비 PJ 와이어프레이밍</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스마트문화앱 UX 설계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10/27(월)
-작품발표회</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도깨비 PJ UI 디자인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도깨비 PJ 프로토타이핑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1차 제출 피드백 보완</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1차 상세코딩
-2차 주제선정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쉐도잉 PJ 차기작 준비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스마트문화앱 UI 디자인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11/18(화)
-수료식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작품발표회
-(10/27)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>디지털디자인 사후관리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로그래밍 언어 응용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6/26(목)
-입학식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1차 프로토타이핑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2차 PJ 상세코딩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2차 산출물작업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCS 학습단위</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도깨비 PJ 상세코딩</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 쉐도잉 프로젝트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>디자인 구성요소 제작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>디자인 구성요소 설계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>디자인 구성요소 응용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(디지털디자인)UIUX 반응형 웹디자인 &amp; 웹퍼블리셔(디자인&amp;코딩) 양성 C 1회차 주별 상세일정</x:t>
+    <x:t>사용자 리서치
+평가(9/16)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사용자 리서치
+스마트문화앱 UX 설계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>디자인 구성요소 설계
+디자인 구성요소 제작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>디자인 구성요소 제작
+디자인 구성요소 응용</x:t>
   </x:si>
   <x:si>
     <x:t>프로그래밍 
@@ -284,90 +296,91 @@
 평가(10/24)</x:t>
   </x:si>
   <x:si>
-    <x:t>디자인 구성요소 설계
-디자인 구성요소 제작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사용자 리서치
-스마트문화앱 UX 설계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>디자인 구성요소 제작
-디자인 구성요소 응용</x:t>
+    <x:t>16주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0-1주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0-2주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0-3주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1차 주제선정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과목평가일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공식 프로젝트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15주차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20주차</x:t>
   </x:si>
   <x:si>
     <x:t>11주차</x:t>
   </x:si>
   <x:si>
-    <x:t>12주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18주차</x:t>
+    <x:t>1차 상세코딩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22주차</x:t>
   </x:si>
   <x:si>
     <x:t>기술훈련일정</x:t>
   </x:si>
   <x:si>
-    <x:t>20주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21주차</x:t>
-  </x:si>
-  <x:si>
     <x:t>준비단계</x:t>
   </x:si>
   <x:si>
-    <x:t>19주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0-2주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0-3주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공식 프로젝트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>과목평가일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1차 주제선정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0-1주차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1차 상세코딩</x:t>
+    <x:t>서비스ㆍ경험디자인 시나리오개발
+사용자 리서치</x:t>
   </x:si>
   <x:si>
     <x:t>시안 디자인 개발 심화
 서비스ㆍ경험디자인 관찰조사</x:t>
   </x:si>
   <x:si>
-    <x:t>서비스ㆍ경험디자인 시나리오개발
-사용자 리서치</x:t>
+    <x:t>보그 PJ 상세코딩
+산리오 PJ 분석/설계(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>디자인 구성요소
+설계 및 제작
+평가(8/4)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1차 상세코딩
+2차 PJ 디자인 &amp; 프로토타입</x:t>
   </x:si>
   <x:si>
     <x:t>스마트문화앱 UI 디자인
@@ -393,19 +406,6 @@
   <x:si>
     <x:t>프로젝트 완료 최종보고
 디지털디자인 사후관리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1차 상세코딩
-2차 PJ 디자인 &amp; 프로토타입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보그 PJ 상세코딩
-산리오 PJ 분석/설계(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>디자인 구성요소
-설계 및 제작
-평가(8/4)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -417,7 +417,7 @@
     <x:numFmt numFmtId="165" formatCode="&quot;총&quot;\ #\ &quot;일&quot;"/>
     <x:numFmt numFmtId="166" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;\ aaa&quot;요일&quot;"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:name val="맑은 고딕"/>
       <x:sz val="11"/>
@@ -449,11 +449,6 @@
       <x:color rgb="ff000000"/>
     </x:font>
     <x:font>
-      <x:name val="나눔명조"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
       <x:name val="맑은 고딕"/>
       <x:sz val="14"/>
       <x:color rgb="ff000000"/>
@@ -465,12 +460,23 @@
       <x:color rgb="ff000000"/>
       <x:b val="1"/>
     </x:font>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="14"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="8"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:font hs:extension="1">
           <x:name val="맑은 고딕"/>
-          <x:sz val="14"/>
+          <x:sz val="20"/>
           <x:color rgb="ff000000"/>
+          <x:b val="1"/>
           <hs:size val="100"/>
           <hs:ratio val="100"/>
           <hs:spacing val="0"/>
@@ -480,22 +486,12 @@
       <mc:Fallback>
         <x:font>
           <x:name val="맑은 고딕"/>
-          <x:sz val="14"/>
+          <x:sz val="20"/>
           <x:color rgb="ff000000"/>
+          <x:b val="1"/>
         </x:font>
       </mc:Fallback>
     </mc:AlternateContent>
-    <x:font>
-      <x:name val="맑은 고딕"/>
-      <x:sz val="8"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="맑은 고딕"/>
-      <x:sz val="20"/>
-      <x:color rgb="ff000000"/>
-      <x:b val="1"/>
-    </x:font>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:font hs:extension="1">
@@ -517,7 +513,7 @@
       </mc:Fallback>
     </mc:AlternateContent>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -568,12 +564,6 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffccecff"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="ffb7dee8"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
@@ -743,7 +733,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="62">
+  <x:cellXfs count="54">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -773,60 +763,60 @@
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+        <x:xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
@@ -885,13 +875,13 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center" wrapText="1"/>
         </x:xf>
       </mc:Fallback>
@@ -911,92 +901,14 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+        <x:xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
@@ -1013,7 +925,7 @@
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
-    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -1252,143 +1164,156 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="14" fontId="7" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="14" fontId="7" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="14" fontId="7" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="14" fontId="7" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
+          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
         <x:xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="14" fontId="8" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="14" fontId="8" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="164" fontId="0" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="164" fontId="0" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="14" fontId="8" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="14" fontId="8" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
@@ -1396,96 +1321,57 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="11" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="11" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="11" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="11" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="11" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="11" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="166" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="166" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="0" fontId="10" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="10" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="10" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="10" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="10" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="10" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="166" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="166" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
@@ -1806,72 +1692,72 @@
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="2:12" ht="53.25" customHeight="1">
-      <x:c r="B2" s="55" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C2" s="56"/>
-      <x:c r="D2" s="56"/>
-      <x:c r="E2" s="56"/>
-      <x:c r="F2" s="56"/>
-      <x:c r="G2" s="56"/>
-      <x:c r="H2" s="56"/>
-      <x:c r="I2" s="56"/>
-      <x:c r="J2" s="56"/>
-      <x:c r="K2" s="56"/>
-      <x:c r="L2" s="57"/>
+      <x:c r="B2" s="50" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C2" s="51"/>
+      <x:c r="D2" s="51"/>
+      <x:c r="E2" s="51"/>
+      <x:c r="F2" s="51"/>
+      <x:c r="G2" s="51"/>
+      <x:c r="H2" s="51"/>
+      <x:c r="I2" s="51"/>
+      <x:c r="J2" s="51"/>
+      <x:c r="K2" s="51"/>
+      <x:c r="L2" s="52"/>
     </x:row>
     <x:row r="3" spans="2:11" ht="18.75" customHeight="1">
-      <x:c r="B3" s="51"/>
-      <x:c r="C3" s="51"/>
-      <x:c r="D3" s="51"/>
-      <x:c r="E3" s="51"/>
-      <x:c r="F3" s="51"/>
-      <x:c r="G3" s="51"/>
-      <x:c r="H3" s="51"/>
-      <x:c r="I3" s="51"/>
-      <x:c r="J3" s="51"/>
-      <x:c r="K3" s="51"/>
+      <x:c r="B3" s="46"/>
+      <x:c r="C3" s="46"/>
+      <x:c r="D3" s="46"/>
+      <x:c r="E3" s="46"/>
+      <x:c r="F3" s="46"/>
+      <x:c r="G3" s="46"/>
+      <x:c r="H3" s="46"/>
+      <x:c r="I3" s="46"/>
+      <x:c r="J3" s="46"/>
+      <x:c r="K3" s="46"/>
     </x:row>
     <x:row r="4" spans="2:12" s="3" customFormat="1" ht="34.5" customHeight="1">
       <x:c r="B4" s="8" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C4" s="52" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D4" s="52"/>
-      <x:c r="E4" s="52"/>
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C4" s="47" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D4" s="47"/>
+      <x:c r="E4" s="47"/>
       <x:c r="F4" s="7" t="s">
-        <x:v>15</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G4" s="7" t="s">
-        <x:v>65</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H4" s="7" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="I4" s="7" t="s">
-        <x:v>67</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K4" s="7" t="s">
-        <x:v>80</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="L4" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="2:12" s="3" customFormat="1" ht="48" hidden="1" customHeight="1">
       <x:c r="B5" s="9" t="s">
-        <x:v>96</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C5" s="10">
         <x:v>45561</x:v>
       </x:c>
       <x:c r="D5" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E5" s="10">
         <x:v>45562</x:v>
@@ -1881,25 +1767,25 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G5" s="13" t="s">
-        <x:v>38</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H5" s="11"/>
       <x:c r="I5" s="11"/>
       <x:c r="J5" s="11"/>
       <x:c r="K5" s="14" t="s">
-        <x:v>40</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="L5" s="15"/>
     </x:row>
     <x:row r="6" spans="2:12" s="3" customFormat="1" ht="48" hidden="1" customHeight="1">
       <x:c r="B6" s="9" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C6" s="10">
         <x:v>45565</x:v>
       </x:c>
       <x:c r="D6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E6" s="10">
         <x:v>45569</x:v>
@@ -1909,25 +1795,25 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="G6" s="13" t="s">
-        <x:v>38</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H6" s="11"/>
       <x:c r="I6" s="11"/>
       <x:c r="J6" s="11"/>
       <x:c r="K6" s="14" t="s">
-        <x:v>40</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="L6" s="15"/>
     </x:row>
     <x:row r="7" spans="2:12" s="3" customFormat="1" ht="48" hidden="1" customHeight="1">
       <x:c r="B7" s="9" t="s">
-        <x:v>90</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C7" s="10">
         <x:v>45572</x:v>
       </x:c>
       <x:c r="D7" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E7" s="10">
         <x:v>45573</x:v>
@@ -1937,741 +1823,741 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G7" s="13" t="s">
-        <x:v>38</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H7" s="11"/>
       <x:c r="I7" s="11"/>
       <x:c r="J7" s="11"/>
       <x:c r="K7" s="14" t="s">
-        <x:v>40</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="L7" s="15"/>
     </x:row>
     <x:row r="8" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B8" s="29" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C8" s="30">
+      <x:c r="B8" s="23" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C8" s="24">
         <x:v>45834</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E8" s="30">
+      <x:c r="D8" s="25" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E8" s="24">
         <x:v>45835</x:v>
       </x:c>
-      <x:c r="F8" s="32">
+      <x:c r="F8" s="26">
         <x:f>DAYS360(C8,E8)+1</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G8" s="33" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H8" s="31"/>
-      <x:c r="I8" s="31"/>
-      <x:c r="J8" s="31"/>
-      <x:c r="K8" s="34" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="L8" s="35" t="s">
-        <x:v>61</x:v>
+      <x:c r="G8" s="27" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H8" s="25"/>
+      <x:c r="I8" s="25"/>
+      <x:c r="J8" s="25"/>
+      <x:c r="K8" s="28" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L8" s="29" t="s">
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B9" s="36" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="37">
+      <x:c r="B9" s="30" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C9" s="31">
         <x:v>45838</x:v>
       </x:c>
-      <x:c r="D9" s="38" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E9" s="37">
+      <x:c r="D9" s="32" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E9" s="31">
         <x:v>45842</x:v>
       </x:c>
-      <x:c r="F9" s="39">
+      <x:c r="F9" s="33">
         <x:f t="shared" ref="F9:F27" si="0">DAYS360(C9,E9)+1</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G9" s="33" t="s">
+      <x:c r="G9" s="27" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="H9" s="40"/>
-      <x:c r="I9" s="38" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="J9" s="38" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="K9" s="41" t="s">
+      <x:c r="H9" s="34"/>
+      <x:c r="I9" s="32" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="L9" s="42"/>
+      <x:c r="J9" s="32" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="K9" s="35" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L9" s="36"/>
     </x:row>
     <x:row r="10" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B10" s="36" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C10" s="37">
+      <x:c r="B10" s="30" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C10" s="31">
         <x:v>45845</x:v>
       </x:c>
-      <x:c r="D10" s="38" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E10" s="37">
+      <x:c r="D10" s="32" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E10" s="31">
         <x:v>45849</x:v>
       </x:c>
-      <x:c r="F10" s="39">
+      <x:c r="F10" s="33">
         <x:f t="shared" si="0"/>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G10" s="33" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H10" s="40"/>
-      <x:c r="I10" s="38" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="J10" s="38" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="K10" s="41" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="L10" s="42"/>
+      <x:c r="G10" s="27" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H10" s="34"/>
+      <x:c r="I10" s="32" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J10" s="32" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="K10" s="35" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L10" s="36"/>
     </x:row>
     <x:row r="11" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B11" s="36" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="37">
+      <x:c r="B11" s="30" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C11" s="31">
         <x:v>45852</x:v>
       </x:c>
-      <x:c r="D11" s="38" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E11" s="37">
+      <x:c r="D11" s="32" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E11" s="31">
         <x:v>45856</x:v>
       </x:c>
-      <x:c r="F11" s="39">
+      <x:c r="F11" s="33">
         <x:f>DAYS360(C11,E11)+1</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G11" s="33" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H11" s="43"/>
-      <x:c r="I11" s="38" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="J11" s="41" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="K11" s="41" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="L11" s="42"/>
+      <x:c r="G11" s="27" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H11" s="37"/>
+      <x:c r="I11" s="32" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J11" s="35" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="K11" s="35" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L11" s="36"/>
     </x:row>
     <x:row r="12" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B12" s="36" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="37">
+      <x:c r="B12" s="30" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C12" s="31">
         <x:v>45859</x:v>
       </x:c>
-      <x:c r="D12" s="38" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E12" s="37">
+      <x:c r="D12" s="32" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E12" s="31">
         <x:v>45863</x:v>
       </x:c>
-      <x:c r="F12" s="39">
+      <x:c r="F12" s="33">
         <x:f t="shared" si="0"/>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G12" s="33" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H12" s="40"/>
-      <x:c r="I12" s="38" t="s">
+      <x:c r="G12" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H12" s="34"/>
+      <x:c r="I12" s="32" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J12" s="35" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K12" s="35" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L12" s="36"/>
+    </x:row>
+    <x:row r="13" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
+      <x:c r="B13" s="30" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C13" s="31">
+        <x:v>45866</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="J12" s="41" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K12" s="41" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="L12" s="42"/>
-    </x:row>
-    <x:row r="13" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B13" s="36" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C13" s="37">
-        <x:v>45866</x:v>
-      </x:c>
-      <x:c r="D13" s="38" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E13" s="37">
+      <x:c r="E13" s="31">
         <x:v>45867</x:v>
       </x:c>
-      <x:c r="F13" s="39">
+      <x:c r="F13" s="33">
         <x:f t="shared" si="0"/>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G13" s="33" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H13" s="40"/>
-      <x:c r="I13" s="38" t="s">
+      <x:c r="G13" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H13" s="34"/>
+      <x:c r="I13" s="32" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J13" s="35" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K13" s="35" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L13" s="36"/>
+    </x:row>
+    <x:row r="14" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
+      <x:c r="B14" s="30" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C14" s="31">
+        <x:v>45873</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="J13" s="41" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K13" s="41" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="L13" s="42"/>
-    </x:row>
-    <x:row r="14" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B14" s="36" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C14" s="37">
-        <x:v>45873</x:v>
-      </x:c>
-      <x:c r="D14" s="38" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E14" s="37">
+      <x:c r="E14" s="31">
         <x:v>45877</x:v>
       </x:c>
-      <x:c r="F14" s="39">
+      <x:c r="F14" s="33">
         <x:f>DAYS360(C14,E14)+1</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G14" s="33" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H14" s="44" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="I14" s="41" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="J14" s="41" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="K14" s="41" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="L14" s="35"/>
+      <x:c r="G14" s="27" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H14" s="38" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="I14" s="35" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J14" s="35" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K14" s="35" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L14" s="29"/>
     </x:row>
     <x:row r="15" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B15" s="36" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C15" s="37">
+      <x:c r="B15" s="30" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C15" s="31">
         <x:v>45880</x:v>
       </x:c>
-      <x:c r="D15" s="38" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E15" s="37">
+      <x:c r="D15" s="32" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E15" s="31">
         <x:v>45883</x:v>
       </x:c>
-      <x:c r="F15" s="39">
+      <x:c r="F15" s="33">
         <x:f>DAYS360(C15,E15)+1</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G15" s="33" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H15" s="40"/>
-      <x:c r="I15" s="41" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="J15" s="38" t="s">
+      <x:c r="G15" s="27" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="H15" s="34"/>
+      <x:c r="I15" s="35" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J15" s="32" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K15" s="35" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="L15" s="36"/>
+    </x:row>
+    <x:row r="16" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
+      <x:c r="B16" s="30" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="K15" s="41" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="L15" s="42"/>
-    </x:row>
-    <x:row r="16" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B16" s="36" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C16" s="37">
+      <x:c r="C16" s="31">
         <x:v>45887</x:v>
       </x:c>
-      <x:c r="D16" s="38" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E16" s="37">
+      <x:c r="D16" s="32" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E16" s="31">
         <x:v>45891</x:v>
       </x:c>
-      <x:c r="F16" s="39">
+      <x:c r="F16" s="33">
         <x:f t="shared" si="0"/>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G16" s="33" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H16" s="40"/>
-      <x:c r="I16" s="41" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J16" s="38" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="K16" s="41" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="L16" s="42"/>
+      <x:c r="G16" s="27" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H16" s="34"/>
+      <x:c r="I16" s="35" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J16" s="32" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K16" s="35" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L16" s="36"/>
     </x:row>
     <x:row r="17" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B17" s="36" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C17" s="37">
+      <x:c r="B17" s="30" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C17" s="31">
         <x:v>45894</x:v>
       </x:c>
-      <x:c r="D17" s="38" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E17" s="37">
+      <x:c r="D17" s="32" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E17" s="31">
         <x:v>45898</x:v>
       </x:c>
-      <x:c r="F17" s="39">
+      <x:c r="F17" s="33">
         <x:f>DAYS360(C17,E17)+1</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G17" s="33" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="H17" s="44" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="I17" s="41" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J17" s="41" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="K17" s="41" t="s">
+      <x:c r="G17" s="27" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H17" s="38" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I17" s="35" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J17" s="35" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="L17" s="35" t="s">
-        <x:v>43</x:v>
+      <x:c r="K17" s="35" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L17" s="29" t="s">
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B18" s="36" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C18" s="37">
+      <x:c r="B18" s="30" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C18" s="31">
         <x:v>45901</x:v>
       </x:c>
-      <x:c r="D18" s="38" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E18" s="37">
+      <x:c r="D18" s="32" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E18" s="31">
         <x:v>45905</x:v>
       </x:c>
-      <x:c r="F18" s="39">
+      <x:c r="F18" s="33">
         <x:f>DAYS360(C18,E18)+1</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G18" s="33" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H18" s="40"/>
-      <x:c r="I18" s="41" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J18" s="41" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="K18" s="41" t="s">
+      <x:c r="G18" s="27" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H18" s="34"/>
+      <x:c r="I18" s="35" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J18" s="35" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="L18" s="42"/>
+      <x:c r="K18" s="35" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L18" s="36"/>
     </x:row>
     <x:row r="19" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B19" s="36" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C19" s="37">
+      <x:c r="B19" s="30" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C19" s="31">
         <x:v>45908</x:v>
       </x:c>
-      <x:c r="D19" s="38" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E19" s="37">
+      <x:c r="D19" s="32" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E19" s="31">
         <x:v>45912</x:v>
       </x:c>
-      <x:c r="F19" s="39">
+      <x:c r="F19" s="33">
         <x:f>DAYS360(C19,E19)+1</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G19" s="33" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H19" s="44" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="I19" s="41" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J19" s="41" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="K19" s="41" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="L19" s="42"/>
+      <x:c r="G19" s="27" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H19" s="38" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="I19" s="35" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="J19" s="35" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="K19" s="35" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L19" s="36"/>
     </x:row>
     <x:row r="20" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B20" s="36" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C20" s="37">
+      <x:c r="B20" s="30" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C20" s="31">
         <x:v>45915</x:v>
       </x:c>
-      <x:c r="D20" s="38" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E20" s="37">
+      <x:c r="D20" s="32" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E20" s="31">
         <x:v>45919</x:v>
       </x:c>
-      <x:c r="F20" s="39">
+      <x:c r="F20" s="33">
         <x:f>DAYS360(C20,E20)+1</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G20" s="33" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="H20" s="48" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="I20" s="41" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="J20" s="41" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="K20" s="41" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="L20" s="42"/>
+      <x:c r="G20" s="27" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H20" s="41" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="I20" s="35" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J20" s="35" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="K20" s="35" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L20" s="36"/>
     </x:row>
     <x:row r="21" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B21" s="36" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C21" s="37">
+      <x:c r="B21" s="30" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C21" s="31">
         <x:v>45922</x:v>
       </x:c>
-      <x:c r="D21" s="38" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E21" s="37">
+      <x:c r="D21" s="32" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E21" s="31">
         <x:v>45926</x:v>
       </x:c>
-      <x:c r="F21" s="39">
+      <x:c r="F21" s="33">
         <x:f t="shared" si="0"/>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G21" s="33" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H21" s="40"/>
-      <x:c r="I21" s="41" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="J21" s="41" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="K21" s="41" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L21" s="42"/>
+      <x:c r="G21" s="27" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H21" s="34"/>
+      <x:c r="I21" s="35" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J21" s="35" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="K21" s="35" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="L21" s="36"/>
     </x:row>
     <x:row r="22" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B22" s="36" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C22" s="37">
+      <x:c r="B22" s="30" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C22" s="31">
         <x:v>45929</x:v>
       </x:c>
-      <x:c r="D22" s="38" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E22" s="37">
+      <x:c r="D22" s="32" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E22" s="31">
         <x:v>45932</x:v>
       </x:c>
-      <x:c r="F22" s="39">
+      <x:c r="F22" s="33">
         <x:f t="shared" si="0"/>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G22" s="33" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H22" s="40"/>
-      <x:c r="I22" s="41" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="J22" s="41" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="K22" s="41" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="L22" s="42"/>
+      <x:c r="G22" s="27" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H22" s="34"/>
+      <x:c r="I22" s="35" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J22" s="35" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="K22" s="35" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="L22" s="36"/>
     </x:row>
     <x:row r="23" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B23" s="36" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C23" s="37">
+      <x:c r="B23" s="30" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C23" s="31">
         <x:v>45940</x:v>
       </x:c>
-      <x:c r="D23" s="38" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E23" s="37">
+      <x:c r="D23" s="32" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E23" s="31">
         <x:v>45940</x:v>
       </x:c>
-      <x:c r="F23" s="39">
+      <x:c r="F23" s="33">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G23" s="33" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H23" s="40"/>
-      <x:c r="I23" s="41" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="J23" s="41" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="K23" s="41" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="L23" s="42"/>
+      <x:c r="G23" s="27" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H23" s="34"/>
+      <x:c r="I23" s="35" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J23" s="35" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K23" s="35" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="L23" s="36"/>
     </x:row>
     <x:row r="24" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B24" s="36" t="s">
+      <x:c r="B24" s="30" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C24" s="37">
+      <x:c r="C24" s="31">
         <x:v>45943</x:v>
       </x:c>
-      <x:c r="D24" s="38" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E24" s="37">
+      <x:c r="D24" s="32" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E24" s="31">
         <x:v>45947</x:v>
       </x:c>
-      <x:c r="F24" s="39">
+      <x:c r="F24" s="33">
         <x:f>DAYS360(C24,E24)+1</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G24" s="33" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H24" s="48" t="s">
+      <x:c r="G24" s="27" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H24" s="41" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="I24" s="35" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J24" s="35" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="I24" s="41" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="J24" s="41" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="K24" s="41" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="L24" s="42"/>
+      <x:c r="K24" s="35" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="L24" s="36"/>
     </x:row>
     <x:row r="25" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B25" s="36" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C25" s="37">
+      <x:c r="B25" s="30" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C25" s="31">
         <x:v>45950</x:v>
       </x:c>
-      <x:c r="D25" s="38" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E25" s="37">
+      <x:c r="D25" s="32" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E25" s="31">
         <x:v>45954</x:v>
       </x:c>
-      <x:c r="F25" s="39">
+      <x:c r="F25" s="33">
         <x:f t="shared" si="0"/>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G25" s="33" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H25" s="48" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="I25" s="40" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="J25" s="41" t="s">
+      <x:c r="G25" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H25" s="41" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="I25" s="34" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J25" s="35" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="K25" s="35" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="K25" s="41" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="L25" s="42"/>
+      <x:c r="L25" s="36"/>
     </x:row>
     <x:row r="26" spans="2:12" s="3" customFormat="1" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B26" s="36" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C26" s="37">
+      <x:c r="B26" s="30" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C26" s="31">
         <x:v>45957</x:v>
       </x:c>
-      <x:c r="D26" s="38" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E26" s="37">
+      <x:c r="D26" s="32" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E26" s="31">
         <x:v>45961</x:v>
       </x:c>
-      <x:c r="F26" s="39">
+      <x:c r="F26" s="33">
         <x:f t="shared" si="0"/>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G26" s="33" t="s">
+      <x:c r="G26" s="27" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H26" s="42" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I26" s="34" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J26" s="35" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H26" s="49" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="I26" s="40" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="J26" s="41" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="K26" s="41" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="L26" s="50" t="s">
-        <x:v>50</x:v>
+      <x:c r="K26" s="35" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="L26" s="43" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="2:12" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B27" s="36" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C27" s="37">
+      <x:c r="B27" s="30" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C27" s="31">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="D27" s="38" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E27" s="37">
+      <x:c r="D27" s="32" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E27" s="31">
         <x:v>45968</x:v>
       </x:c>
-      <x:c r="F27" s="39">
+      <x:c r="F27" s="33">
         <x:f t="shared" si="0"/>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G27" s="33" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H27" s="48" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="I27" s="34" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="J27" s="38" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="K27" s="41" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="L27" s="61"/>
-    </x:row>
-    <x:row r="28" spans="1:12" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="A28" s="23"/>
-      <x:c r="B28" s="24" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="C28" s="25">
+      <x:c r="G27" s="27" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H27" s="41" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="I27" s="28" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J27" s="32" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K27" s="35" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="L27" s="45"/>
+    </x:row>
+    <x:row r="28" spans="2:12" ht="56.45000000000000284217" customHeight="1">
+      <x:c r="B28" s="30" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C28" s="31">
         <x:v>45971</x:v>
       </x:c>
-      <x:c r="D28" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E28" s="25">
+      <x:c r="D28" s="32" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E28" s="31">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="F28" s="27">
+      <x:c r="F28" s="33">
         <x:f>DAYS360(C28,E28)+1</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G28" s="22" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H28" s="58"/>
-      <x:c r="I28" s="59" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J28" s="26" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="K28" s="28" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="L28" s="60"/>
-    </x:row>
-    <x:row r="29" spans="2:12" ht="56.45000000000000284217" customHeight="1">
-      <x:c r="B29" s="17" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C29" s="18">
+      <x:c r="G28" s="27" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H28" s="53"/>
+      <x:c r="I28" s="25" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J28" s="32" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K28" s="35" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="L28" s="29"/>
+    </x:row>
+    <x:row r="29" spans="1:12" ht="56.45000000000000284217" customHeight="1">
+      <x:c r="A29" s="17"/>
+      <x:c r="B29" s="18" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C29" s="19">
         <x:v>45978</x:v>
       </x:c>
-      <x:c r="D29" s="19" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E29" s="18">
+      <x:c r="D29" s="20" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E29" s="19">
         <x:v>45979</x:v>
       </x:c>
-      <x:c r="F29" s="47">
+      <x:c r="F29" s="21">
         <x:f>DAYS360(C29,E29)+1</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="G29" s="16" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H29" s="46" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="I29" s="20" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="J29" s="19" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="K29" s="21" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="L29" s="45" t="s">
-        <x:v>57</x:v>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H29" s="40" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I29" s="44" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="J29" s="20" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K29" s="22" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="L29" s="39" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="3:6" ht="47.25" customHeight="1">
@@ -2683,36 +2569,36 @@
       </x:c>
     </x:row>
     <x:row r="31" spans="2:11" ht="21.75" customHeight="1">
-      <x:c r="B31" s="53" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C31" s="53"/>
-      <x:c r="D31" s="53"/>
-      <x:c r="E31" s="53"/>
-      <x:c r="F31" s="53"/>
-      <x:c r="G31" s="53"/>
-      <x:c r="H31" s="53"/>
-      <x:c r="I31" s="53"/>
-      <x:c r="J31" s="53"/>
-      <x:c r="K31" s="53"/>
+      <x:c r="B31" s="48" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C31" s="48"/>
+      <x:c r="D31" s="48"/>
+      <x:c r="E31" s="48"/>
+      <x:c r="F31" s="48"/>
+      <x:c r="G31" s="48"/>
+      <x:c r="H31" s="48"/>
+      <x:c r="I31" s="48"/>
+      <x:c r="J31" s="48"/>
+      <x:c r="K31" s="48"/>
     </x:row>
     <x:row r="32" spans="2:11" s="5" customFormat="1" ht="26.35000000000000142109">
-      <x:c r="B32" s="54" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C32" s="54"/>
-      <x:c r="D32" s="54"/>
-      <x:c r="E32" s="54"/>
-      <x:c r="F32" s="54"/>
-      <x:c r="G32" s="54"/>
-      <x:c r="H32" s="54"/>
-      <x:c r="I32" s="54"/>
-      <x:c r="J32" s="54"/>
-      <x:c r="K32" s="54"/>
+      <x:c r="B32" s="49" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C32" s="49"/>
+      <x:c r="D32" s="49"/>
+      <x:c r="E32" s="49"/>
+      <x:c r="F32" s="49"/>
+      <x:c r="G32" s="49"/>
+      <x:c r="H32" s="49"/>
+      <x:c r="I32" s="49"/>
+      <x:c r="J32" s="49"/>
+      <x:c r="K32" s="49"/>
     </x:row>
     <x:row r="43" spans="9:9">
       <x:c r="I43" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2723,7 +2609,7 @@
     <x:mergeCell ref="B32:K32"/>
     <x:mergeCell ref="B2:L2"/>
   </x:mergeCells>
-  <x:pageMargins left="0.69999998807907104492" right="0.69999998807907104492" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="39" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
@@ -2734,7 +2620,7 @@
   <x:dimension ref="A1:A1"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.89999999999999857891"/>
   <x:sheetData/>
-  <x:pageMargins left="0.69999998807907104492" right="0.69999998807907104492" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -2745,7 +2631,7 @@
   <x:dimension ref="A1:A1"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.89999999999999857891"/>
   <x:sheetData/>
-  <x:pageMargins left="0.69999998807907104492" right="0.69999998807907104492" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>